--- a/AdapsChip/ChipUI/Input/Swan01_ROISRAM_Excel.xlsx
+++ b/AdapsChip/ChipUI/Input/Swan01_ROISRAM_Excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Adaps\AdapsChip\ChipUI\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363B75EA-4502-4FC4-AE7E-A5C5D920A3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46737E4F-ADCF-48D0-AF5D-713E757038CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="6" r:id="rId1"/>
@@ -5101,14 +5101,13 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5116,13 +5115,14 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5408,16 +5408,16 @@
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.5" style="15" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="10" customWidth="1"/>
     <col min="3" max="3" width="9" style="2"/>
     <col min="11" max="11" width="63.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16"/>
       <c r="C1" s="1" t="s">
         <v>37</v>
       </c>
@@ -5450,7 +5450,7 @@
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="11" t="s">
         <v>36</v>
       </c>
       <c r="C2" s="4">
@@ -5482,10 +5482,10 @@
       </c>
     </row>
     <row r="3" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C3" s="4">
@@ -5515,8 +5515,8 @@
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C4" s="4">
@@ -5546,8 +5546,8 @@
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="4">
@@ -5577,8 +5577,8 @@
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C6" s="4">
@@ -5608,8 +5608,8 @@
       <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C7" s="4">
@@ -5639,8 +5639,8 @@
       <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="4">
@@ -5670,8 +5670,8 @@
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="17"/>
+      <c r="B9" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C9" s="4">
@@ -5701,8 +5701,8 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C10" s="4">
@@ -5732,8 +5732,8 @@
       <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="9" t="s">
         <v>58</v>
       </c>
       <c r="C11" s="4">
@@ -5763,8 +5763,8 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="4">
@@ -5794,8 +5794,8 @@
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C13" s="4">
@@ -5825,8 +5825,8 @@
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
-      <c r="B14" s="14" t="s">
+      <c r="A14" s="17"/>
+      <c r="B14" s="9" t="s">
         <v>61</v>
       </c>
       <c r="C14" s="4">
@@ -5856,8 +5856,8 @@
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="17"/>
+      <c r="B15" s="9" t="s">
         <v>62</v>
       </c>
       <c r="C15" s="4">
@@ -5887,8 +5887,8 @@
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="17"/>
+      <c r="B16" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C16" s="4">
@@ -5918,8 +5918,8 @@
       <c r="K16" s="6"/>
     </row>
     <row r="17" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="17"/>
+      <c r="B17" s="9" t="s">
         <v>64</v>
       </c>
       <c r="C17" s="4">
@@ -5949,8 +5949,8 @@
       <c r="K17" s="6"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
-      <c r="B18" s="14" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="9" t="s">
         <v>65</v>
       </c>
       <c r="C18" s="4">
@@ -5983,7 +5983,7 @@
       <c r="A19" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -6016,7 +6016,7 @@
       <c r="A20" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C20" s="4">
@@ -6049,7 +6049,7 @@
       <c r="A21" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="9" t="s">
         <v>68</v>
       </c>
       <c r="C21" s="4">
@@ -6082,7 +6082,7 @@
       <c r="A22" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C22" s="4">
@@ -6117,7 +6117,7 @@
       <c r="A23" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="9" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -6150,7 +6150,7 @@
       <c r="A24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="9" t="s">
         <v>71</v>
       </c>
       <c r="C24" s="4">
@@ -6183,7 +6183,7 @@
       <c r="A25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C25" s="4">
@@ -6213,10 +6213,10 @@
       <c r="K25" s="6"/>
     </row>
     <row r="26" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C26" s="4">
@@ -6246,8 +6246,8 @@
       <c r="K26" s="6"/>
     </row>
     <row r="27" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14" t="s">
+      <c r="A27" s="14"/>
+      <c r="B27" s="9" t="s">
         <v>74</v>
       </c>
       <c r="C27" s="4">
@@ -6277,8 +6277,8 @@
       <c r="K27" s="6"/>
     </row>
     <row r="28" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14" t="s">
+      <c r="A28" s="14"/>
+      <c r="B28" s="9" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="4">
@@ -6308,8 +6308,8 @@
       <c r="K28" s="6"/>
     </row>
     <row r="29" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14" t="s">
+      <c r="A29" s="14"/>
+      <c r="B29" s="9" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="4">
@@ -6339,8 +6339,8 @@
       <c r="K29" s="6"/>
     </row>
     <row r="30" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14" t="s">
+      <c r="A30" s="14"/>
+      <c r="B30" s="9" t="s">
         <v>77</v>
       </c>
       <c r="C30" s="4">
@@ -6370,8 +6370,8 @@
       <c r="K30" s="6"/>
     </row>
     <row r="31" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14" t="s">
+      <c r="A31" s="14"/>
+      <c r="B31" s="9" t="s">
         <v>78</v>
       </c>
       <c r="C31" s="4">
@@ -6401,8 +6401,8 @@
       <c r="K31" s="6"/>
     </row>
     <row r="32" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14" t="s">
+      <c r="A32" s="14"/>
+      <c r="B32" s="9" t="s">
         <v>79</v>
       </c>
       <c r="C32" s="4">
@@ -6432,8 +6432,8 @@
       <c r="K32" s="6"/>
     </row>
     <row r="33" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14" t="s">
+      <c r="A33" s="14"/>
+      <c r="B33" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C33" s="4">
@@ -6463,8 +6463,8 @@
       <c r="K33" s="6"/>
     </row>
     <row r="34" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14" t="s">
+      <c r="A34" s="14"/>
+      <c r="B34" s="9" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="4">
@@ -6494,8 +6494,8 @@
       <c r="K34" s="6"/>
     </row>
     <row r="35" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="9" t="s">
         <v>82</v>
       </c>
       <c r="C35" s="4">
@@ -6525,8 +6525,8 @@
       <c r="K35" s="6"/>
     </row>
     <row r="36" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14" t="s">
+      <c r="A36" s="14"/>
+      <c r="B36" s="9" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="4">
@@ -6556,8 +6556,8 @@
       <c r="K36" s="6"/>
     </row>
     <row r="37" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14" t="s">
+      <c r="A37" s="14"/>
+      <c r="B37" s="9" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="4">
@@ -6587,8 +6587,8 @@
       <c r="K37" s="6"/>
     </row>
     <row r="38" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14" t="s">
+      <c r="A38" s="14"/>
+      <c r="B38" s="9" t="s">
         <v>85</v>
       </c>
       <c r="C38" s="4">
@@ -6618,8 +6618,8 @@
       <c r="K38" s="6"/>
     </row>
     <row r="39" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14" t="s">
+      <c r="A39" s="14"/>
+      <c r="B39" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C39" s="4">
@@ -6649,8 +6649,8 @@
       <c r="K39" s="6"/>
     </row>
     <row r="40" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="9" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="4">
@@ -6680,8 +6680,8 @@
       <c r="K40" s="6"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" s="10"/>
-      <c r="B41" s="14" t="s">
+      <c r="A41" s="15"/>
+      <c r="B41" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C41" s="4">
@@ -6711,10 +6711,10 @@
       <c r="K41" s="6"/>
     </row>
     <row r="42" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C42" s="4">
@@ -6744,8 +6744,8 @@
       <c r="K42" s="6"/>
     </row>
     <row r="43" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14" t="s">
+      <c r="A43" s="14"/>
+      <c r="B43" s="9" t="s">
         <v>90</v>
       </c>
       <c r="C43" s="4">
@@ -6775,8 +6775,8 @@
       <c r="K43" s="6"/>
     </row>
     <row r="44" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14" t="s">
+      <c r="A44" s="14"/>
+      <c r="B44" s="9" t="s">
         <v>91</v>
       </c>
       <c r="C44" s="4">
@@ -6806,8 +6806,8 @@
       <c r="K44" s="6"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="10"/>
-      <c r="B45" s="14" t="s">
+      <c r="A45" s="15"/>
+      <c r="B45" s="9" t="s">
         <v>92</v>
       </c>
       <c r="C45" s="4">
@@ -6837,10 +6837,10 @@
       <c r="K45" s="6"/>
     </row>
     <row r="46" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="9" t="s">
         <v>93</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -6870,8 +6870,8 @@
       <c r="K46" s="6"/>
     </row>
     <row r="47" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14" t="s">
+      <c r="A47" s="14"/>
+      <c r="B47" s="9" t="s">
         <v>94</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -6901,8 +6901,8 @@
       <c r="K47" s="6"/>
     </row>
     <row r="48" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14" t="s">
+      <c r="A48" s="14"/>
+      <c r="B48" s="9" t="s">
         <v>95</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -6932,8 +6932,8 @@
       <c r="K48" s="6"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" s="10"/>
-      <c r="B49" s="14" t="s">
+      <c r="A49" s="15"/>
+      <c r="B49" s="9" t="s">
         <v>96</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -6963,10 +6963,10 @@
       <c r="K49" s="6"/>
     </row>
     <row r="50" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="4">
@@ -6996,8 +6996,8 @@
       <c r="K50" s="6"/>
     </row>
     <row r="51" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14" t="s">
+      <c r="A51" s="14"/>
+      <c r="B51" s="9" t="s">
         <v>98</v>
       </c>
       <c r="C51" s="4">
@@ -7027,8 +7027,8 @@
       <c r="K51" s="6"/>
     </row>
     <row r="52" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14" t="s">
+      <c r="A52" s="14"/>
+      <c r="B52" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C52" s="4">
@@ -7058,8 +7058,8 @@
       <c r="K52" s="6"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="10"/>
-      <c r="B53" s="14" t="s">
+      <c r="A53" s="15"/>
+      <c r="B53" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C53" s="4">
@@ -7089,10 +7089,10 @@
       <c r="K53" s="6"/>
     </row>
     <row r="54" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="4">
@@ -7122,8 +7122,8 @@
       <c r="K54" s="6"/>
     </row>
     <row r="55" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14" t="s">
+      <c r="A55" s="14"/>
+      <c r="B55" s="9" t="s">
         <v>98</v>
       </c>
       <c r="C55" s="4">
@@ -7153,8 +7153,8 @@
       <c r="K55" s="6"/>
     </row>
     <row r="56" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14" t="s">
+      <c r="A56" s="14"/>
+      <c r="B56" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C56" s="4">
@@ -7184,8 +7184,8 @@
       <c r="K56" s="6"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="10"/>
-      <c r="B57" s="14" t="s">
+      <c r="A57" s="15"/>
+      <c r="B57" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C57" s="4">
@@ -7215,10 +7215,10 @@
       <c r="K57" s="6"/>
     </row>
     <row r="58" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C58" s="4">
@@ -7248,8 +7248,8 @@
       <c r="K58" s="6"/>
     </row>
     <row r="59" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14" t="s">
+      <c r="A59" s="14"/>
+      <c r="B59" s="9" t="s">
         <v>102</v>
       </c>
       <c r="C59" s="4">
@@ -7279,8 +7279,8 @@
       <c r="K59" s="6"/>
     </row>
     <row r="60" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14" t="s">
+      <c r="A60" s="14"/>
+      <c r="B60" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C60" s="4">
@@ -7310,8 +7310,8 @@
       <c r="K60" s="6"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14" t="s">
+      <c r="A61" s="14"/>
+      <c r="B61" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C61" s="4">
@@ -7341,10 +7341,10 @@
       <c r="K61" s="6"/>
     </row>
     <row r="62" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C62" s="4">
@@ -7374,8 +7374,8 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14" t="s">
+      <c r="A63" s="14"/>
+      <c r="B63" s="9" t="s">
         <v>102</v>
       </c>
       <c r="C63" s="4">
@@ -7405,8 +7405,8 @@
       <c r="K63" s="6"/>
     </row>
     <row r="64" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14" t="s">
+      <c r="A64" s="14"/>
+      <c r="B64" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C64" s="4">
@@ -7436,8 +7436,8 @@
       <c r="K64" s="6"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14" t="s">
+      <c r="A65" s="14"/>
+      <c r="B65" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="4">
@@ -7467,10 +7467,10 @@
       <c r="K65" s="6"/>
     </row>
     <row r="66" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="9" t="s">
         <v>101</v>
       </c>
       <c r="C66" s="4">
@@ -7500,8 +7500,8 @@
       <c r="K66" s="6"/>
     </row>
     <row r="67" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14" t="s">
+      <c r="A67" s="14"/>
+      <c r="B67" s="9" t="s">
         <v>102</v>
       </c>
       <c r="C67" s="4">
@@ -7531,8 +7531,8 @@
       <c r="K67" s="6"/>
     </row>
     <row r="68" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14" t="s">
+      <c r="A68" s="14"/>
+      <c r="B68" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C68" s="4">
@@ -7562,8 +7562,8 @@
       <c r="K68" s="6"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14" t="s">
+      <c r="A69" s="14"/>
+      <c r="B69" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C69" s="4">
@@ -7593,10 +7593,10 @@
       <c r="K69" s="6"/>
     </row>
     <row r="70" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="9" t="s">
         <v>105</v>
       </c>
       <c r="C70" s="4">
@@ -7626,8 +7626,8 @@
       <c r="K70" s="6"/>
     </row>
     <row r="71" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14" t="s">
+      <c r="A71" s="14"/>
+      <c r="B71" s="9" t="s">
         <v>106</v>
       </c>
       <c r="C71" s="4">
@@ -7657,8 +7657,8 @@
       <c r="K71" s="6"/>
     </row>
     <row r="72" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14" t="s">
+      <c r="A72" s="14"/>
+      <c r="B72" s="9" t="s">
         <v>107</v>
       </c>
       <c r="C72" s="4">
@@ -7688,8 +7688,8 @@
       <c r="K72" s="6"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14" t="s">
+      <c r="A73" s="14"/>
+      <c r="B73" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C73" s="4">
@@ -7719,10 +7719,10 @@
       <c r="K73" s="6"/>
     </row>
     <row r="74" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="9" t="s">
         <v>109</v>
       </c>
       <c r="C74" s="4">
@@ -7752,8 +7752,8 @@
       <c r="K74" s="6"/>
     </row>
     <row r="75" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="11"/>
-      <c r="B75" s="14" t="s">
+      <c r="A75" s="17"/>
+      <c r="B75" s="9" t="s">
         <v>110</v>
       </c>
       <c r="C75" s="4">
@@ -7783,8 +7783,8 @@
       <c r="K75" s="6"/>
     </row>
     <row r="76" spans="1:11" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="11"/>
-      <c r="B76" s="14" t="s">
+      <c r="A76" s="17"/>
+      <c r="B76" s="9" t="s">
         <v>111</v>
       </c>
       <c r="C76" s="4">
@@ -7814,8 +7814,8 @@
       <c r="K76" s="6"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="11"/>
-      <c r="B77" s="14" t="s">
+      <c r="A77" s="17"/>
+      <c r="B77" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C77" s="4">
@@ -7845,10 +7845,10 @@
       <c r="K77" s="6"/>
     </row>
     <row r="78" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="9" t="s">
         <v>234</v>
       </c>
       <c r="C78" s="4" t="s">
@@ -7878,8 +7878,8 @@
       <c r="K78" s="6"/>
     </row>
     <row r="79" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="14" t="s">
+      <c r="A79" s="17"/>
+      <c r="B79" s="9" t="s">
         <v>235</v>
       </c>
       <c r="C79" s="4" t="s">
@@ -7909,8 +7909,8 @@
       <c r="K79" s="6"/>
     </row>
     <row r="80" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A80" s="11"/>
-      <c r="B80" s="14" t="s">
+      <c r="A80" s="17"/>
+      <c r="B80" s="9" t="s">
         <v>236</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -7940,8 +7940,8 @@
       <c r="K80" s="6"/>
     </row>
     <row r="81" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A81" s="11"/>
-      <c r="B81" s="14" t="s">
+      <c r="A81" s="17"/>
+      <c r="B81" s="9" t="s">
         <v>237</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -7971,8 +7971,8 @@
       <c r="K81" s="6"/>
     </row>
     <row r="82" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A82" s="11"/>
-      <c r="B82" s="14" t="s">
+      <c r="A82" s="17"/>
+      <c r="B82" s="9" t="s">
         <v>238</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -8002,8 +8002,8 @@
       <c r="K82" s="6"/>
     </row>
     <row r="83" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A83" s="11"/>
-      <c r="B83" s="14" t="s">
+      <c r="A83" s="17"/>
+      <c r="B83" s="9" t="s">
         <v>239</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -8033,8 +8033,8 @@
       <c r="K83" s="6"/>
     </row>
     <row r="84" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A84" s="11"/>
-      <c r="B84" s="14" t="s">
+      <c r="A84" s="17"/>
+      <c r="B84" s="9" t="s">
         <v>240</v>
       </c>
       <c r="C84" s="4" t="s">
@@ -8064,8 +8064,8 @@
       <c r="K84" s="6"/>
     </row>
     <row r="85" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A85" s="11"/>
-      <c r="B85" s="14" t="s">
+      <c r="A85" s="17"/>
+      <c r="B85" s="9" t="s">
         <v>241</v>
       </c>
       <c r="C85" s="4" t="s">
@@ -8095,8 +8095,8 @@
       <c r="K85" s="6"/>
     </row>
     <row r="86" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A86" s="11"/>
-      <c r="B86" s="14" t="s">
+      <c r="A86" s="17"/>
+      <c r="B86" s="9" t="s">
         <v>242</v>
       </c>
       <c r="C86" s="4" t="s">
@@ -8126,8 +8126,8 @@
       <c r="K86" s="6"/>
     </row>
     <row r="87" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A87" s="11"/>
-      <c r="B87" s="14" t="s">
+      <c r="A87" s="17"/>
+      <c r="B87" s="9" t="s">
         <v>243</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -8157,8 +8157,8 @@
       <c r="K87" s="6"/>
     </row>
     <row r="88" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A88" s="11"/>
-      <c r="B88" s="14" t="s">
+      <c r="A88" s="17"/>
+      <c r="B88" s="9" t="s">
         <v>244</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -8188,8 +8188,8 @@
       <c r="K88" s="6"/>
     </row>
     <row r="89" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A89" s="11"/>
-      <c r="B89" s="14" t="s">
+      <c r="A89" s="17"/>
+      <c r="B89" s="9" t="s">
         <v>245</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -8219,8 +8219,8 @@
       <c r="K89" s="6"/>
     </row>
     <row r="90" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A90" s="11"/>
-      <c r="B90" s="14" t="s">
+      <c r="A90" s="17"/>
+      <c r="B90" s="9" t="s">
         <v>246</v>
       </c>
       <c r="C90" s="4" t="s">
@@ -8250,8 +8250,8 @@
       <c r="K90" s="6"/>
     </row>
     <row r="91" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A91" s="11"/>
-      <c r="B91" s="14" t="s">
+      <c r="A91" s="17"/>
+      <c r="B91" s="9" t="s">
         <v>247</v>
       </c>
       <c r="C91" s="4" t="s">
@@ -8281,8 +8281,8 @@
       <c r="K91" s="6"/>
     </row>
     <row r="92" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A92" s="11"/>
-      <c r="B92" s="14" t="s">
+      <c r="A92" s="17"/>
+      <c r="B92" s="9" t="s">
         <v>248</v>
       </c>
       <c r="C92" s="4" t="s">
@@ -8312,8 +8312,8 @@
       <c r="K92" s="6"/>
     </row>
     <row r="93" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A93" s="11"/>
-      <c r="B93" s="14" t="s">
+      <c r="A93" s="17"/>
+      <c r="B93" s="9" t="s">
         <v>249</v>
       </c>
       <c r="C93" s="4" t="s">
@@ -8343,8 +8343,8 @@
       <c r="K93" s="6"/>
     </row>
     <row r="94" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A94" s="11"/>
-      <c r="B94" s="14" t="s">
+      <c r="A94" s="17"/>
+      <c r="B94" s="9" t="s">
         <v>250</v>
       </c>
       <c r="C94" s="4" t="s">
@@ -8374,8 +8374,8 @@
       <c r="K94" s="6"/>
     </row>
     <row r="95" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A95" s="11"/>
-      <c r="B95" s="14" t="s">
+      <c r="A95" s="17"/>
+      <c r="B95" s="9" t="s">
         <v>251</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -8405,8 +8405,8 @@
       <c r="K95" s="6"/>
     </row>
     <row r="96" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A96" s="11"/>
-      <c r="B96" s="14" t="s">
+      <c r="A96" s="17"/>
+      <c r="B96" s="9" t="s">
         <v>252</v>
       </c>
       <c r="C96" s="4" t="s">
@@ -8436,8 +8436,8 @@
       <c r="K96" s="6"/>
     </row>
     <row r="97" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A97" s="11"/>
-      <c r="B97" s="14" t="s">
+      <c r="A97" s="17"/>
+      <c r="B97" s="9" t="s">
         <v>253</v>
       </c>
       <c r="C97" s="4" t="s">
@@ -8467,8 +8467,8 @@
       <c r="K97" s="6"/>
     </row>
     <row r="98" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A98" s="11"/>
-      <c r="B98" s="14" t="s">
+      <c r="A98" s="17"/>
+      <c r="B98" s="9" t="s">
         <v>254</v>
       </c>
       <c r="C98" s="4" t="s">
@@ -8498,8 +8498,8 @@
       <c r="K98" s="6"/>
     </row>
     <row r="99" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A99" s="11"/>
-      <c r="B99" s="14" t="s">
+      <c r="A99" s="17"/>
+      <c r="B99" s="9" t="s">
         <v>255</v>
       </c>
       <c r="C99" s="4" t="s">
@@ -8529,8 +8529,8 @@
       <c r="K99" s="6"/>
     </row>
     <row r="100" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A100" s="11"/>
-      <c r="B100" s="14" t="s">
+      <c r="A100" s="17"/>
+      <c r="B100" s="9" t="s">
         <v>256</v>
       </c>
       <c r="C100" s="4" t="s">
@@ -8560,8 +8560,8 @@
       <c r="K100" s="6"/>
     </row>
     <row r="101" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A101" s="11"/>
-      <c r="B101" s="14" t="s">
+      <c r="A101" s="17"/>
+      <c r="B101" s="9" t="s">
         <v>257</v>
       </c>
       <c r="C101" s="4" t="s">
@@ -8591,8 +8591,8 @@
       <c r="K101" s="6"/>
     </row>
     <row r="102" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A102" s="11"/>
-      <c r="B102" s="14" t="s">
+      <c r="A102" s="17"/>
+      <c r="B102" s="9" t="s">
         <v>258</v>
       </c>
       <c r="C102" s="4" t="s">
@@ -8622,8 +8622,8 @@
       <c r="K102" s="6"/>
     </row>
     <row r="103" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A103" s="11"/>
-      <c r="B103" s="14" t="s">
+      <c r="A103" s="17"/>
+      <c r="B103" s="9" t="s">
         <v>259</v>
       </c>
       <c r="C103" s="4" t="s">
@@ -8653,8 +8653,8 @@
       <c r="K103" s="6"/>
     </row>
     <row r="104" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A104" s="11"/>
-      <c r="B104" s="14" t="s">
+      <c r="A104" s="17"/>
+      <c r="B104" s="9" t="s">
         <v>260</v>
       </c>
       <c r="C104" s="4" t="s">
@@ -8684,8 +8684,8 @@
       <c r="K104" s="6"/>
     </row>
     <row r="105" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A105" s="11"/>
-      <c r="B105" s="14" t="s">
+      <c r="A105" s="17"/>
+      <c r="B105" s="9" t="s">
         <v>261</v>
       </c>
       <c r="C105" s="4" t="s">
@@ -8715,8 +8715,8 @@
       <c r="K105" s="6"/>
     </row>
     <row r="106" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A106" s="11"/>
-      <c r="B106" s="14" t="s">
+      <c r="A106" s="17"/>
+      <c r="B106" s="9" t="s">
         <v>262</v>
       </c>
       <c r="C106" s="4" t="s">
@@ -8746,8 +8746,8 @@
       <c r="K106" s="6"/>
     </row>
     <row r="107" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A107" s="11"/>
-      <c r="B107" s="14" t="s">
+      <c r="A107" s="17"/>
+      <c r="B107" s="9" t="s">
         <v>263</v>
       </c>
       <c r="C107" s="4" t="s">
@@ -8777,8 +8777,8 @@
       <c r="K107" s="6"/>
     </row>
     <row r="108" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A108" s="11"/>
-      <c r="B108" s="14" t="s">
+      <c r="A108" s="17"/>
+      <c r="B108" s="9" t="s">
         <v>264</v>
       </c>
       <c r="C108" s="4" t="s">
@@ -8808,8 +8808,8 @@
       <c r="K108" s="6"/>
     </row>
     <row r="109" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A109" s="11"/>
-      <c r="B109" s="14" t="s">
+      <c r="A109" s="17"/>
+      <c r="B109" s="9" t="s">
         <v>265</v>
       </c>
       <c r="C109" s="4" t="s">
@@ -8839,8 +8839,8 @@
       <c r="K109" s="6"/>
     </row>
     <row r="110" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A110" s="11"/>
-      <c r="B110" s="14" t="s">
+      <c r="A110" s="17"/>
+      <c r="B110" s="9" t="s">
         <v>266</v>
       </c>
       <c r="C110" s="4" t="s">
@@ -8870,8 +8870,8 @@
       <c r="K110" s="6"/>
     </row>
     <row r="111" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A111" s="11"/>
-      <c r="B111" s="14" t="s">
+      <c r="A111" s="17"/>
+      <c r="B111" s="9" t="s">
         <v>267</v>
       </c>
       <c r="C111" s="4" t="s">
@@ -8901,8 +8901,8 @@
       <c r="K111" s="6"/>
     </row>
     <row r="112" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A112" s="11"/>
-      <c r="B112" s="14" t="s">
+      <c r="A112" s="17"/>
+      <c r="B112" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C112" s="4" t="s">
@@ -8932,8 +8932,8 @@
       <c r="K112" s="6"/>
     </row>
     <row r="113" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A113" s="11"/>
-      <c r="B113" s="14" t="s">
+      <c r="A113" s="17"/>
+      <c r="B113" s="9" t="s">
         <v>269</v>
       </c>
       <c r="C113" s="4" t="s">
@@ -8963,8 +8963,8 @@
       <c r="K113" s="6"/>
     </row>
     <row r="114" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A114" s="11"/>
-      <c r="B114" s="14" t="s">
+      <c r="A114" s="17"/>
+      <c r="B114" s="9" t="s">
         <v>270</v>
       </c>
       <c r="C114" s="4" t="s">
@@ -8994,8 +8994,8 @@
       <c r="K114" s="6"/>
     </row>
     <row r="115" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A115" s="11"/>
-      <c r="B115" s="14" t="s">
+      <c r="A115" s="17"/>
+      <c r="B115" s="9" t="s">
         <v>271</v>
       </c>
       <c r="C115" s="4" t="s">
@@ -9025,8 +9025,8 @@
       <c r="K115" s="6"/>
     </row>
     <row r="116" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A116" s="11"/>
-      <c r="B116" s="14" t="s">
+      <c r="A116" s="17"/>
+      <c r="B116" s="9" t="s">
         <v>272</v>
       </c>
       <c r="C116" s="4" t="s">
@@ -9056,8 +9056,8 @@
       <c r="K116" s="6"/>
     </row>
     <row r="117" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A117" s="11"/>
-      <c r="B117" s="14" t="s">
+      <c r="A117" s="17"/>
+      <c r="B117" s="9" t="s">
         <v>273</v>
       </c>
       <c r="C117" s="4" t="s">
@@ -9087,8 +9087,8 @@
       <c r="K117" s="6"/>
     </row>
     <row r="118" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A118" s="11"/>
-      <c r="B118" s="14" t="s">
+      <c r="A118" s="17"/>
+      <c r="B118" s="9" t="s">
         <v>274</v>
       </c>
       <c r="C118" s="4" t="s">
@@ -9118,8 +9118,8 @@
       <c r="K118" s="6"/>
     </row>
     <row r="119" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A119" s="11"/>
-      <c r="B119" s="14" t="s">
+      <c r="A119" s="17"/>
+      <c r="B119" s="9" t="s">
         <v>275</v>
       </c>
       <c r="C119" s="4" t="s">
@@ -9149,8 +9149,8 @@
       <c r="K119" s="6"/>
     </row>
     <row r="120" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A120" s="11"/>
-      <c r="B120" s="14" t="s">
+      <c r="A120" s="17"/>
+      <c r="B120" s="9" t="s">
         <v>276</v>
       </c>
       <c r="C120" s="4" t="s">
@@ -9180,8 +9180,8 @@
       <c r="K120" s="6"/>
     </row>
     <row r="121" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A121" s="11"/>
-      <c r="B121" s="14" t="s">
+      <c r="A121" s="17"/>
+      <c r="B121" s="9" t="s">
         <v>277</v>
       </c>
       <c r="C121" s="4" t="s">
@@ -9211,8 +9211,8 @@
       <c r="K121" s="6"/>
     </row>
     <row r="122" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A122" s="11"/>
-      <c r="B122" s="14" t="s">
+      <c r="A122" s="17"/>
+      <c r="B122" s="9" t="s">
         <v>278</v>
       </c>
       <c r="C122" s="4" t="s">
@@ -9242,8 +9242,8 @@
       <c r="K122" s="6"/>
     </row>
     <row r="123" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A123" s="11"/>
-      <c r="B123" s="14" t="s">
+      <c r="A123" s="17"/>
+      <c r="B123" s="9" t="s">
         <v>279</v>
       </c>
       <c r="C123" s="4" t="s">
@@ -9273,8 +9273,8 @@
       <c r="K123" s="6"/>
     </row>
     <row r="124" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A124" s="11"/>
-      <c r="B124" s="14" t="s">
+      <c r="A124" s="17"/>
+      <c r="B124" s="9" t="s">
         <v>280</v>
       </c>
       <c r="C124" s="4" t="s">
@@ -9304,8 +9304,8 @@
       <c r="K124" s="6"/>
     </row>
     <row r="125" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A125" s="11"/>
-      <c r="B125" s="14" t="s">
+      <c r="A125" s="17"/>
+      <c r="B125" s="9" t="s">
         <v>281</v>
       </c>
       <c r="C125" s="4" t="s">
@@ -9335,8 +9335,8 @@
       <c r="K125" s="6"/>
     </row>
     <row r="126" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A126" s="11"/>
-      <c r="B126" s="14" t="s">
+      <c r="A126" s="17"/>
+      <c r="B126" s="9" t="s">
         <v>282</v>
       </c>
       <c r="C126" s="4" t="s">
@@ -9366,8 +9366,8 @@
       <c r="K126" s="6"/>
     </row>
     <row r="127" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A127" s="11"/>
-      <c r="B127" s="14" t="s">
+      <c r="A127" s="17"/>
+      <c r="B127" s="9" t="s">
         <v>283</v>
       </c>
       <c r="C127" s="4" t="s">
@@ -9397,8 +9397,8 @@
       <c r="K127" s="6"/>
     </row>
     <row r="128" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A128" s="11"/>
-      <c r="B128" s="14" t="s">
+      <c r="A128" s="17"/>
+      <c r="B128" s="9" t="s">
         <v>284</v>
       </c>
       <c r="C128" s="4" t="s">
@@ -9428,8 +9428,8 @@
       <c r="K128" s="6"/>
     </row>
     <row r="129" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A129" s="11"/>
-      <c r="B129" s="14" t="s">
+      <c r="A129" s="17"/>
+      <c r="B129" s="9" t="s">
         <v>285</v>
       </c>
       <c r="C129" s="4" t="s">
@@ -9459,8 +9459,8 @@
       <c r="K129" s="6"/>
     </row>
     <row r="130" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A130" s="11"/>
-      <c r="B130" s="14" t="s">
+      <c r="A130" s="17"/>
+      <c r="B130" s="9" t="s">
         <v>286</v>
       </c>
       <c r="C130" s="4" t="s">
@@ -9490,8 +9490,8 @@
       <c r="K130" s="6"/>
     </row>
     <row r="131" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A131" s="11"/>
-      <c r="B131" s="14" t="s">
+      <c r="A131" s="17"/>
+      <c r="B131" s="9" t="s">
         <v>287</v>
       </c>
       <c r="C131" s="4" t="s">
@@ -9521,8 +9521,8 @@
       <c r="K131" s="6"/>
     </row>
     <row r="132" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A132" s="11"/>
-      <c r="B132" s="14" t="s">
+      <c r="A132" s="17"/>
+      <c r="B132" s="9" t="s">
         <v>288</v>
       </c>
       <c r="C132" s="4" t="s">
@@ -9552,8 +9552,8 @@
       <c r="K132" s="6"/>
     </row>
     <row r="133" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A133" s="11"/>
-      <c r="B133" s="14" t="s">
+      <c r="A133" s="17"/>
+      <c r="B133" s="9" t="s">
         <v>289</v>
       </c>
       <c r="C133" s="4" t="s">
@@ -9583,8 +9583,8 @@
       <c r="K133" s="6"/>
     </row>
     <row r="134" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A134" s="11"/>
-      <c r="B134" s="14" t="s">
+      <c r="A134" s="17"/>
+      <c r="B134" s="9" t="s">
         <v>290</v>
       </c>
       <c r="C134" s="4" t="s">
@@ -9614,8 +9614,8 @@
       <c r="K134" s="6"/>
     </row>
     <row r="135" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A135" s="11"/>
-      <c r="B135" s="14" t="s">
+      <c r="A135" s="17"/>
+      <c r="B135" s="9" t="s">
         <v>291</v>
       </c>
       <c r="C135" s="4" t="s">
@@ -9645,8 +9645,8 @@
       <c r="K135" s="6"/>
     </row>
     <row r="136" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A136" s="11"/>
-      <c r="B136" s="14" t="s">
+      <c r="A136" s="17"/>
+      <c r="B136" s="9" t="s">
         <v>292</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -9676,8 +9676,8 @@
       <c r="K136" s="6"/>
     </row>
     <row r="137" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A137" s="11"/>
-      <c r="B137" s="14" t="s">
+      <c r="A137" s="17"/>
+      <c r="B137" s="9" t="s">
         <v>293</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -9707,8 +9707,8 @@
       <c r="K137" s="6"/>
     </row>
     <row r="138" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A138" s="11"/>
-      <c r="B138" s="14" t="s">
+      <c r="A138" s="17"/>
+      <c r="B138" s="9" t="s">
         <v>294</v>
       </c>
       <c r="C138" s="4" t="s">
@@ -9738,8 +9738,8 @@
       <c r="K138" s="6"/>
     </row>
     <row r="139" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A139" s="11"/>
-      <c r="B139" s="14" t="s">
+      <c r="A139" s="17"/>
+      <c r="B139" s="9" t="s">
         <v>295</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -9769,8 +9769,8 @@
       <c r="K139" s="6"/>
     </row>
     <row r="140" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A140" s="11"/>
-      <c r="B140" s="14" t="s">
+      <c r="A140" s="17"/>
+      <c r="B140" s="9" t="s">
         <v>296</v>
       </c>
       <c r="C140" s="4" t="s">
@@ -9800,8 +9800,8 @@
       <c r="K140" s="6"/>
     </row>
     <row r="141" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A141" s="11"/>
-      <c r="B141" s="14" t="s">
+      <c r="A141" s="17"/>
+      <c r="B141" s="9" t="s">
         <v>297</v>
       </c>
       <c r="C141" s="4" t="s">
@@ -9831,8 +9831,8 @@
       <c r="K141" s="6"/>
     </row>
     <row r="142" spans="1:11" ht="15" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="11"/>
-      <c r="B142" s="14" t="s">
+      <c r="A142" s="17"/>
+      <c r="B142" s="9" t="s">
         <v>298</v>
       </c>
       <c r="C142" s="4" t="s">
@@ -9862,8 +9862,8 @@
       <c r="K142" s="6"/>
     </row>
     <row r="143" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A143" s="11"/>
-      <c r="B143" s="14" t="s">
+      <c r="A143" s="17"/>
+      <c r="B143" s="9" t="s">
         <v>299</v>
       </c>
       <c r="C143" s="4" t="s">
@@ -9893,8 +9893,8 @@
       <c r="K143" s="6"/>
     </row>
     <row r="144" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A144" s="11"/>
-      <c r="B144" s="14" t="s">
+      <c r="A144" s="17"/>
+      <c r="B144" s="9" t="s">
         <v>300</v>
       </c>
       <c r="C144" s="4" t="s">
@@ -9924,8 +9924,8 @@
       <c r="K144" s="6"/>
     </row>
     <row r="145" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A145" s="11"/>
-      <c r="B145" s="14" t="s">
+      <c r="A145" s="17"/>
+      <c r="B145" s="9" t="s">
         <v>301</v>
       </c>
       <c r="C145" s="4" t="s">
@@ -9955,8 +9955,8 @@
       <c r="K145" s="6"/>
     </row>
     <row r="146" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A146" s="11"/>
-      <c r="B146" s="14" t="s">
+      <c r="A146" s="17"/>
+      <c r="B146" s="9" t="s">
         <v>302</v>
       </c>
       <c r="C146" s="4" t="s">
@@ -9986,8 +9986,8 @@
       <c r="K146" s="6"/>
     </row>
     <row r="147" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A147" s="11"/>
-      <c r="B147" s="14" t="s">
+      <c r="A147" s="17"/>
+      <c r="B147" s="9" t="s">
         <v>303</v>
       </c>
       <c r="C147" s="4" t="s">
@@ -10017,8 +10017,8 @@
       <c r="K147" s="6"/>
     </row>
     <row r="148" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A148" s="11"/>
-      <c r="B148" s="14" t="s">
+      <c r="A148" s="17"/>
+      <c r="B148" s="9" t="s">
         <v>304</v>
       </c>
       <c r="C148" s="4" t="s">
@@ -10048,8 +10048,8 @@
       <c r="K148" s="6"/>
     </row>
     <row r="149" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A149" s="11"/>
-      <c r="B149" s="14" t="s">
+      <c r="A149" s="17"/>
+      <c r="B149" s="9" t="s">
         <v>305</v>
       </c>
       <c r="C149" s="4" t="s">
@@ -10079,8 +10079,8 @@
       <c r="K149" s="6"/>
     </row>
     <row r="150" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A150" s="11"/>
-      <c r="B150" s="14" t="s">
+      <c r="A150" s="17"/>
+      <c r="B150" s="9" t="s">
         <v>306</v>
       </c>
       <c r="C150" s="4" t="s">
@@ -10110,8 +10110,8 @@
       <c r="K150" s="6"/>
     </row>
     <row r="151" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A151" s="11"/>
-      <c r="B151" s="14" t="s">
+      <c r="A151" s="17"/>
+      <c r="B151" s="9" t="s">
         <v>307</v>
       </c>
       <c r="C151" s="4" t="s">
@@ -10141,8 +10141,8 @@
       <c r="K151" s="6"/>
     </row>
     <row r="152" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A152" s="11"/>
-      <c r="B152" s="14" t="s">
+      <c r="A152" s="17"/>
+      <c r="B152" s="9" t="s">
         <v>308</v>
       </c>
       <c r="C152" s="4" t="s">
@@ -10172,8 +10172,8 @@
       <c r="K152" s="6"/>
     </row>
     <row r="153" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A153" s="11"/>
-      <c r="B153" s="14" t="s">
+      <c r="A153" s="17"/>
+      <c r="B153" s="9" t="s">
         <v>309</v>
       </c>
       <c r="C153" s="4" t="s">
@@ -10203,8 +10203,8 @@
       <c r="K153" s="6"/>
     </row>
     <row r="154" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A154" s="11"/>
-      <c r="B154" s="14" t="s">
+      <c r="A154" s="17"/>
+      <c r="B154" s="9" t="s">
         <v>310</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -10234,8 +10234,8 @@
       <c r="K154" s="6"/>
     </row>
     <row r="155" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A155" s="11"/>
-      <c r="B155" s="14" t="s">
+      <c r="A155" s="17"/>
+      <c r="B155" s="9" t="s">
         <v>311</v>
       </c>
       <c r="C155" s="4" t="s">
@@ -10265,8 +10265,8 @@
       <c r="K155" s="6"/>
     </row>
     <row r="156" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A156" s="11"/>
-      <c r="B156" s="14" t="s">
+      <c r="A156" s="17"/>
+      <c r="B156" s="9" t="s">
         <v>312</v>
       </c>
       <c r="C156" s="4" t="s">
@@ -10296,8 +10296,8 @@
       <c r="K156" s="6"/>
     </row>
     <row r="157" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A157" s="11"/>
-      <c r="B157" s="14" t="s">
+      <c r="A157" s="17"/>
+      <c r="B157" s="9" t="s">
         <v>313</v>
       </c>
       <c r="C157" s="4" t="s">
@@ -10327,8 +10327,8 @@
       <c r="K157" s="6"/>
     </row>
     <row r="158" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A158" s="11"/>
-      <c r="B158" s="14" t="s">
+      <c r="A158" s="17"/>
+      <c r="B158" s="9" t="s">
         <v>314</v>
       </c>
       <c r="C158" s="4" t="s">
@@ -10358,8 +10358,8 @@
       <c r="K158" s="6"/>
     </row>
     <row r="159" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A159" s="11"/>
-      <c r="B159" s="14" t="s">
+      <c r="A159" s="17"/>
+      <c r="B159" s="9" t="s">
         <v>315</v>
       </c>
       <c r="C159" s="4" t="s">
@@ -10389,8 +10389,8 @@
       <c r="K159" s="6"/>
     </row>
     <row r="160" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A160" s="11"/>
-      <c r="B160" s="14" t="s">
+      <c r="A160" s="17"/>
+      <c r="B160" s="9" t="s">
         <v>316</v>
       </c>
       <c r="C160" s="4" t="s">
@@ -10420,8 +10420,8 @@
       <c r="K160" s="6"/>
     </row>
     <row r="161" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A161" s="11"/>
-      <c r="B161" s="14" t="s">
+      <c r="A161" s="17"/>
+      <c r="B161" s="9" t="s">
         <v>317</v>
       </c>
       <c r="C161" s="4" t="s">
@@ -10451,8 +10451,8 @@
       <c r="K161" s="6"/>
     </row>
     <row r="162" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A162" s="11"/>
-      <c r="B162" s="14" t="s">
+      <c r="A162" s="17"/>
+      <c r="B162" s="9" t="s">
         <v>318</v>
       </c>
       <c r="C162" s="4" t="s">
@@ -10482,8 +10482,8 @@
       <c r="K162" s="6"/>
     </row>
     <row r="163" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A163" s="11"/>
-      <c r="B163" s="14" t="s">
+      <c r="A163" s="17"/>
+      <c r="B163" s="9" t="s">
         <v>319</v>
       </c>
       <c r="C163" s="4" t="s">
@@ -10513,8 +10513,8 @@
       <c r="K163" s="6"/>
     </row>
     <row r="164" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A164" s="11"/>
-      <c r="B164" s="14" t="s">
+      <c r="A164" s="17"/>
+      <c r="B164" s="9" t="s">
         <v>320</v>
       </c>
       <c r="C164" s="4" t="s">
@@ -10544,8 +10544,8 @@
       <c r="K164" s="6"/>
     </row>
     <row r="165" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A165" s="11"/>
-      <c r="B165" s="14" t="s">
+      <c r="A165" s="17"/>
+      <c r="B165" s="9" t="s">
         <v>321</v>
       </c>
       <c r="C165" s="4" t="s">
@@ -10575,8 +10575,8 @@
       <c r="K165" s="6"/>
     </row>
     <row r="166" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A166" s="11"/>
-      <c r="B166" s="14" t="s">
+      <c r="A166" s="17"/>
+      <c r="B166" s="9" t="s">
         <v>322</v>
       </c>
       <c r="C166" s="4" t="s">
@@ -10606,8 +10606,8 @@
       <c r="K166" s="6"/>
     </row>
     <row r="167" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A167" s="11"/>
-      <c r="B167" s="14" t="s">
+      <c r="A167" s="17"/>
+      <c r="B167" s="9" t="s">
         <v>323</v>
       </c>
       <c r="C167" s="4" t="s">
@@ -10637,8 +10637,8 @@
       <c r="K167" s="6"/>
     </row>
     <row r="168" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A168" s="11"/>
-      <c r="B168" s="14" t="s">
+      <c r="A168" s="17"/>
+      <c r="B168" s="9" t="s">
         <v>324</v>
       </c>
       <c r="C168" s="4" t="s">
@@ -10668,8 +10668,8 @@
       <c r="K168" s="6"/>
     </row>
     <row r="169" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A169" s="11"/>
-      <c r="B169" s="14" t="s">
+      <c r="A169" s="17"/>
+      <c r="B169" s="9" t="s">
         <v>325</v>
       </c>
       <c r="C169" s="4" t="s">
@@ -10699,8 +10699,8 @@
       <c r="K169" s="6"/>
     </row>
     <row r="170" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A170" s="11"/>
-      <c r="B170" s="14" t="s">
+      <c r="A170" s="17"/>
+      <c r="B170" s="9" t="s">
         <v>326</v>
       </c>
       <c r="C170" s="4" t="s">
@@ -10730,8 +10730,8 @@
       <c r="K170" s="6"/>
     </row>
     <row r="171" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A171" s="11"/>
-      <c r="B171" s="14" t="s">
+      <c r="A171" s="17"/>
+      <c r="B171" s="9" t="s">
         <v>327</v>
       </c>
       <c r="C171" s="4" t="s">
@@ -10761,8 +10761,8 @@
       <c r="K171" s="6"/>
     </row>
     <row r="172" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A172" s="11"/>
-      <c r="B172" s="14" t="s">
+      <c r="A172" s="17"/>
+      <c r="B172" s="9" t="s">
         <v>328</v>
       </c>
       <c r="C172" s="4" t="s">
@@ -10792,8 +10792,8 @@
       <c r="K172" s="6"/>
     </row>
     <row r="173" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A173" s="11"/>
-      <c r="B173" s="14" t="s">
+      <c r="A173" s="17"/>
+      <c r="B173" s="9" t="s">
         <v>329</v>
       </c>
       <c r="C173" s="4" t="s">
@@ -10823,8 +10823,8 @@
       <c r="K173" s="6"/>
     </row>
     <row r="174" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A174" s="11"/>
-      <c r="B174" s="14" t="s">
+      <c r="A174" s="17"/>
+      <c r="B174" s="9" t="s">
         <v>330</v>
       </c>
       <c r="C174" s="4" t="s">
@@ -10854,8 +10854,8 @@
       <c r="K174" s="6"/>
     </row>
     <row r="175" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A175" s="11"/>
-      <c r="B175" s="14" t="s">
+      <c r="A175" s="17"/>
+      <c r="B175" s="9" t="s">
         <v>331</v>
       </c>
       <c r="C175" s="4" t="s">
@@ -10885,8 +10885,8 @@
       <c r="K175" s="6"/>
     </row>
     <row r="176" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A176" s="11"/>
-      <c r="B176" s="14" t="s">
+      <c r="A176" s="17"/>
+      <c r="B176" s="9" t="s">
         <v>332</v>
       </c>
       <c r="C176" s="4" t="s">
@@ -10916,8 +10916,8 @@
       <c r="K176" s="6"/>
     </row>
     <row r="177" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A177" s="11"/>
-      <c r="B177" s="14" t="s">
+      <c r="A177" s="17"/>
+      <c r="B177" s="9" t="s">
         <v>333</v>
       </c>
       <c r="C177" s="4" t="s">
@@ -10947,8 +10947,8 @@
       <c r="K177" s="6"/>
     </row>
     <row r="178" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A178" s="11"/>
-      <c r="B178" s="14" t="s">
+      <c r="A178" s="17"/>
+      <c r="B178" s="9" t="s">
         <v>334</v>
       </c>
       <c r="C178" s="4" t="s">
@@ -10978,8 +10978,8 @@
       <c r="K178" s="6"/>
     </row>
     <row r="179" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A179" s="11"/>
-      <c r="B179" s="14" t="s">
+      <c r="A179" s="17"/>
+      <c r="B179" s="9" t="s">
         <v>335</v>
       </c>
       <c r="C179" s="4" t="s">
@@ -11009,8 +11009,8 @@
       <c r="K179" s="6"/>
     </row>
     <row r="180" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A180" s="11"/>
-      <c r="B180" s="14" t="s">
+      <c r="A180" s="17"/>
+      <c r="B180" s="9" t="s">
         <v>336</v>
       </c>
       <c r="C180" s="4" t="s">
@@ -11040,8 +11040,8 @@
       <c r="K180" s="6"/>
     </row>
     <row r="181" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A181" s="11"/>
-      <c r="B181" s="14" t="s">
+      <c r="A181" s="17"/>
+      <c r="B181" s="9" t="s">
         <v>337</v>
       </c>
       <c r="C181" s="4" t="s">
@@ -11071,8 +11071,8 @@
       <c r="K181" s="6"/>
     </row>
     <row r="182" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A182" s="11"/>
-      <c r="B182" s="14" t="s">
+      <c r="A182" s="17"/>
+      <c r="B182" s="9" t="s">
         <v>338</v>
       </c>
       <c r="C182" s="4" t="s">
@@ -11102,8 +11102,8 @@
       <c r="K182" s="6"/>
     </row>
     <row r="183" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A183" s="11"/>
-      <c r="B183" s="14" t="s">
+      <c r="A183" s="17"/>
+      <c r="B183" s="9" t="s">
         <v>339</v>
       </c>
       <c r="C183" s="4" t="s">
@@ -11133,8 +11133,8 @@
       <c r="K183" s="6"/>
     </row>
     <row r="184" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A184" s="11"/>
-      <c r="B184" s="14" t="s">
+      <c r="A184" s="17"/>
+      <c r="B184" s="9" t="s">
         <v>340</v>
       </c>
       <c r="C184" s="4" t="s">
@@ -11164,8 +11164,8 @@
       <c r="K184" s="6"/>
     </row>
     <row r="185" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A185" s="11"/>
-      <c r="B185" s="14" t="s">
+      <c r="A185" s="17"/>
+      <c r="B185" s="9" t="s">
         <v>341</v>
       </c>
       <c r="C185" s="4" t="s">
@@ -11195,8 +11195,8 @@
       <c r="K185" s="6"/>
     </row>
     <row r="186" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A186" s="11"/>
-      <c r="B186" s="14" t="s">
+      <c r="A186" s="17"/>
+      <c r="B186" s="9" t="s">
         <v>342</v>
       </c>
       <c r="C186" s="4" t="s">
@@ -11226,8 +11226,8 @@
       <c r="K186" s="6"/>
     </row>
     <row r="187" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A187" s="11"/>
-      <c r="B187" s="14" t="s">
+      <c r="A187" s="17"/>
+      <c r="B187" s="9" t="s">
         <v>343</v>
       </c>
       <c r="C187" s="4" t="s">
@@ -11257,8 +11257,8 @@
       <c r="K187" s="6"/>
     </row>
     <row r="188" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A188" s="11"/>
-      <c r="B188" s="14" t="s">
+      <c r="A188" s="17"/>
+      <c r="B188" s="9" t="s">
         <v>344</v>
       </c>
       <c r="C188" s="4" t="s">
@@ -11288,8 +11288,8 @@
       <c r="K188" s="6"/>
     </row>
     <row r="189" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A189" s="11"/>
-      <c r="B189" s="14" t="s">
+      <c r="A189" s="17"/>
+      <c r="B189" s="9" t="s">
         <v>345</v>
       </c>
       <c r="C189" s="4" t="s">
@@ -11319,8 +11319,8 @@
       <c r="K189" s="6"/>
     </row>
     <row r="190" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A190" s="11"/>
-      <c r="B190" s="14" t="s">
+      <c r="A190" s="17"/>
+      <c r="B190" s="9" t="s">
         <v>346</v>
       </c>
       <c r="C190" s="4" t="s">
@@ -11350,8 +11350,8 @@
       <c r="K190" s="6"/>
     </row>
     <row r="191" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A191" s="11"/>
-      <c r="B191" s="14" t="s">
+      <c r="A191" s="17"/>
+      <c r="B191" s="9" t="s">
         <v>347</v>
       </c>
       <c r="C191" s="4" t="s">
@@ -11381,8 +11381,8 @@
       <c r="K191" s="6"/>
     </row>
     <row r="192" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A192" s="11"/>
-      <c r="B192" s="14" t="s">
+      <c r="A192" s="17"/>
+      <c r="B192" s="9" t="s">
         <v>348</v>
       </c>
       <c r="C192" s="4" t="s">
@@ -11412,8 +11412,8 @@
       <c r="K192" s="6"/>
     </row>
     <row r="193" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A193" s="11"/>
-      <c r="B193" s="14" t="s">
+      <c r="A193" s="17"/>
+      <c r="B193" s="9" t="s">
         <v>349</v>
       </c>
       <c r="C193" s="4" t="s">
@@ -11443,8 +11443,8 @@
       <c r="K193" s="6"/>
     </row>
     <row r="194" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A194" s="11"/>
-      <c r="B194" s="14" t="s">
+      <c r="A194" s="17"/>
+      <c r="B194" s="9" t="s">
         <v>350</v>
       </c>
       <c r="C194" s="4" t="s">
@@ -11474,8 +11474,8 @@
       <c r="K194" s="6"/>
     </row>
     <row r="195" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A195" s="11"/>
-      <c r="B195" s="14" t="s">
+      <c r="A195" s="17"/>
+      <c r="B195" s="9" t="s">
         <v>351</v>
       </c>
       <c r="C195" s="4" t="s">
@@ -11505,8 +11505,8 @@
       <c r="K195" s="6"/>
     </row>
     <row r="196" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A196" s="11"/>
-      <c r="B196" s="14" t="s">
+      <c r="A196" s="17"/>
+      <c r="B196" s="9" t="s">
         <v>352</v>
       </c>
       <c r="C196" s="4" t="s">
@@ -11536,8 +11536,8 @@
       <c r="K196" s="6"/>
     </row>
     <row r="197" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A197" s="11"/>
-      <c r="B197" s="14" t="s">
+      <c r="A197" s="17"/>
+      <c r="B197" s="9" t="s">
         <v>353</v>
       </c>
       <c r="C197" s="4" t="s">
@@ -11567,8 +11567,8 @@
       <c r="K197" s="6"/>
     </row>
     <row r="198" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A198" s="11"/>
-      <c r="B198" s="14" t="s">
+      <c r="A198" s="17"/>
+      <c r="B198" s="9" t="s">
         <v>354</v>
       </c>
       <c r="C198" s="4" t="s">
@@ -11598,8 +11598,8 @@
       <c r="K198" s="6"/>
     </row>
     <row r="199" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A199" s="11"/>
-      <c r="B199" s="14" t="s">
+      <c r="A199" s="17"/>
+      <c r="B199" s="9" t="s">
         <v>355</v>
       </c>
       <c r="C199" s="4" t="s">
@@ -11629,8 +11629,8 @@
       <c r="K199" s="6"/>
     </row>
     <row r="200" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A200" s="11"/>
-      <c r="B200" s="14" t="s">
+      <c r="A200" s="17"/>
+      <c r="B200" s="9" t="s">
         <v>356</v>
       </c>
       <c r="C200" s="4" t="s">
@@ -11660,8 +11660,8 @@
       <c r="K200" s="6"/>
     </row>
     <row r="201" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A201" s="11"/>
-      <c r="B201" s="14" t="s">
+      <c r="A201" s="17"/>
+      <c r="B201" s="9" t="s">
         <v>357</v>
       </c>
       <c r="C201" s="4" t="s">
@@ -11691,8 +11691,8 @@
       <c r="K201" s="6"/>
     </row>
     <row r="202" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A202" s="11"/>
-      <c r="B202" s="14" t="s">
+      <c r="A202" s="17"/>
+      <c r="B202" s="9" t="s">
         <v>358</v>
       </c>
       <c r="C202" s="4" t="s">
@@ -11722,8 +11722,8 @@
       <c r="K202" s="6"/>
     </row>
     <row r="203" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A203" s="11"/>
-      <c r="B203" s="14" t="s">
+      <c r="A203" s="17"/>
+      <c r="B203" s="9" t="s">
         <v>359</v>
       </c>
       <c r="C203" s="4" t="s">
@@ -11753,8 +11753,8 @@
       <c r="K203" s="6"/>
     </row>
     <row r="204" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A204" s="11"/>
-      <c r="B204" s="14" t="s">
+      <c r="A204" s="17"/>
+      <c r="B204" s="9" t="s">
         <v>360</v>
       </c>
       <c r="C204" s="4" t="s">
@@ -11784,8 +11784,8 @@
       <c r="K204" s="6"/>
     </row>
     <row r="205" spans="1:11" ht="15" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="11"/>
-      <c r="B205" s="14" t="s">
+      <c r="A205" s="17"/>
+      <c r="B205" s="9" t="s">
         <v>361</v>
       </c>
       <c r="C205" s="4" t="s">
@@ -11815,8 +11815,8 @@
       <c r="K205" s="6"/>
     </row>
     <row r="206" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A206" s="11"/>
-      <c r="B206" s="14" t="s">
+      <c r="A206" s="17"/>
+      <c r="B206" s="9" t="s">
         <v>362</v>
       </c>
       <c r="C206" s="4" t="s">
@@ -11846,8 +11846,8 @@
       <c r="K206" s="6"/>
     </row>
     <row r="207" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A207" s="11"/>
-      <c r="B207" s="14" t="s">
+      <c r="A207" s="17"/>
+      <c r="B207" s="9" t="s">
         <v>363</v>
       </c>
       <c r="C207" s="4" t="s">
@@ -11877,8 +11877,8 @@
       <c r="K207" s="6"/>
     </row>
     <row r="208" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A208" s="11"/>
-      <c r="B208" s="14" t="s">
+      <c r="A208" s="17"/>
+      <c r="B208" s="9" t="s">
         <v>364</v>
       </c>
       <c r="C208" s="4" t="s">
@@ -11908,8 +11908,8 @@
       <c r="K208" s="6"/>
     </row>
     <row r="209" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A209" s="11"/>
-      <c r="B209" s="14" t="s">
+      <c r="A209" s="17"/>
+      <c r="B209" s="9" t="s">
         <v>365</v>
       </c>
       <c r="C209" s="4" t="s">
@@ -11939,8 +11939,8 @@
       <c r="K209" s="6"/>
     </row>
     <row r="210" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A210" s="11"/>
-      <c r="B210" s="14" t="s">
+      <c r="A210" s="17"/>
+      <c r="B210" s="9" t="s">
         <v>366</v>
       </c>
       <c r="C210" s="4" t="s">
@@ -11970,8 +11970,8 @@
       <c r="K210" s="6"/>
     </row>
     <row r="211" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A211" s="11"/>
-      <c r="B211" s="14" t="s">
+      <c r="A211" s="17"/>
+      <c r="B211" s="9" t="s">
         <v>367</v>
       </c>
       <c r="C211" s="4" t="s">
@@ -12001,8 +12001,8 @@
       <c r="K211" s="6"/>
     </row>
     <row r="212" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A212" s="11"/>
-      <c r="B212" s="14" t="s">
+      <c r="A212" s="17"/>
+      <c r="B212" s="9" t="s">
         <v>368</v>
       </c>
       <c r="C212" s="4" t="s">
@@ -12032,8 +12032,8 @@
       <c r="K212" s="6"/>
     </row>
     <row r="213" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A213" s="11"/>
-      <c r="B213" s="14" t="s">
+      <c r="A213" s="17"/>
+      <c r="B213" s="9" t="s">
         <v>369</v>
       </c>
       <c r="C213" s="4" t="s">
@@ -12063,8 +12063,8 @@
       <c r="K213" s="6"/>
     </row>
     <row r="214" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A214" s="11"/>
-      <c r="B214" s="14" t="s">
+      <c r="A214" s="17"/>
+      <c r="B214" s="9" t="s">
         <v>370</v>
       </c>
       <c r="C214" s="4" t="s">
@@ -12094,8 +12094,8 @@
       <c r="K214" s="6"/>
     </row>
     <row r="215" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A215" s="11"/>
-      <c r="B215" s="14" t="s">
+      <c r="A215" s="17"/>
+      <c r="B215" s="9" t="s">
         <v>371</v>
       </c>
       <c r="C215" s="4" t="s">
@@ -12125,8 +12125,8 @@
       <c r="K215" s="6"/>
     </row>
     <row r="216" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A216" s="11"/>
-      <c r="B216" s="14" t="s">
+      <c r="A216" s="17"/>
+      <c r="B216" s="9" t="s">
         <v>372</v>
       </c>
       <c r="C216" s="4" t="s">
@@ -12156,8 +12156,8 @@
       <c r="K216" s="6"/>
     </row>
     <row r="217" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A217" s="11"/>
-      <c r="B217" s="14" t="s">
+      <c r="A217" s="17"/>
+      <c r="B217" s="9" t="s">
         <v>373</v>
       </c>
       <c r="C217" s="4" t="s">
@@ -12187,8 +12187,8 @@
       <c r="K217" s="6"/>
     </row>
     <row r="218" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A218" s="11"/>
-      <c r="B218" s="14" t="s">
+      <c r="A218" s="17"/>
+      <c r="B218" s="9" t="s">
         <v>374</v>
       </c>
       <c r="C218" s="4" t="s">
@@ -12218,8 +12218,8 @@
       <c r="K218" s="6"/>
     </row>
     <row r="219" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A219" s="11"/>
-      <c r="B219" s="14" t="s">
+      <c r="A219" s="17"/>
+      <c r="B219" s="9" t="s">
         <v>375</v>
       </c>
       <c r="C219" s="4" t="s">
@@ -12249,8 +12249,8 @@
       <c r="K219" s="6"/>
     </row>
     <row r="220" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A220" s="11"/>
-      <c r="B220" s="14" t="s">
+      <c r="A220" s="17"/>
+      <c r="B220" s="9" t="s">
         <v>376</v>
       </c>
       <c r="C220" s="4" t="s">
@@ -12280,8 +12280,8 @@
       <c r="K220" s="6"/>
     </row>
     <row r="221" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A221" s="11"/>
-      <c r="B221" s="14" t="s">
+      <c r="A221" s="17"/>
+      <c r="B221" s="9" t="s">
         <v>377</v>
       </c>
       <c r="C221" s="4" t="s">
@@ -12311,8 +12311,8 @@
       <c r="K221" s="6"/>
     </row>
     <row r="222" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A222" s="11"/>
-      <c r="B222" s="14" t="s">
+      <c r="A222" s="17"/>
+      <c r="B222" s="9" t="s">
         <v>378</v>
       </c>
       <c r="C222" s="4" t="s">
@@ -12342,8 +12342,8 @@
       <c r="K222" s="6"/>
     </row>
     <row r="223" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A223" s="11"/>
-      <c r="B223" s="14" t="s">
+      <c r="A223" s="17"/>
+      <c r="B223" s="9" t="s">
         <v>379</v>
       </c>
       <c r="C223" s="4" t="s">
@@ -12373,8 +12373,8 @@
       <c r="K223" s="6"/>
     </row>
     <row r="224" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A224" s="11"/>
-      <c r="B224" s="14" t="s">
+      <c r="A224" s="17"/>
+      <c r="B224" s="9" t="s">
         <v>380</v>
       </c>
       <c r="C224" s="4" t="s">
@@ -12404,8 +12404,8 @@
       <c r="K224" s="6"/>
     </row>
     <row r="225" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A225" s="11"/>
-      <c r="B225" s="14" t="s">
+      <c r="A225" s="17"/>
+      <c r="B225" s="9" t="s">
         <v>381</v>
       </c>
       <c r="C225" s="4" t="s">
@@ -12435,8 +12435,8 @@
       <c r="K225" s="6"/>
     </row>
     <row r="226" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A226" s="11"/>
-      <c r="B226" s="14" t="s">
+      <c r="A226" s="17"/>
+      <c r="B226" s="9" t="s">
         <v>382</v>
       </c>
       <c r="C226" s="4" t="s">
@@ -12466,8 +12466,8 @@
       <c r="K226" s="6"/>
     </row>
     <row r="227" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A227" s="11"/>
-      <c r="B227" s="14" t="s">
+      <c r="A227" s="17"/>
+      <c r="B227" s="9" t="s">
         <v>383</v>
       </c>
       <c r="C227" s="4" t="s">
@@ -12497,8 +12497,8 @@
       <c r="K227" s="6"/>
     </row>
     <row r="228" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A228" s="11"/>
-      <c r="B228" s="14" t="s">
+      <c r="A228" s="17"/>
+      <c r="B228" s="9" t="s">
         <v>384</v>
       </c>
       <c r="C228" s="4" t="s">
@@ -12528,8 +12528,8 @@
       <c r="K228" s="6"/>
     </row>
     <row r="229" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A229" s="11"/>
-      <c r="B229" s="14" t="s">
+      <c r="A229" s="17"/>
+      <c r="B229" s="9" t="s">
         <v>385</v>
       </c>
       <c r="C229" s="4" t="s">
@@ -12559,8 +12559,8 @@
       <c r="K229" s="6"/>
     </row>
     <row r="230" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A230" s="11"/>
-      <c r="B230" s="14" t="s">
+      <c r="A230" s="17"/>
+      <c r="B230" s="9" t="s">
         <v>386</v>
       </c>
       <c r="C230" s="4" t="s">
@@ -12590,8 +12590,8 @@
       <c r="K230" s="6"/>
     </row>
     <row r="231" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A231" s="11"/>
-      <c r="B231" s="14" t="s">
+      <c r="A231" s="17"/>
+      <c r="B231" s="9" t="s">
         <v>387</v>
       </c>
       <c r="C231" s="4" t="s">
@@ -12621,8 +12621,8 @@
       <c r="K231" s="6"/>
     </row>
     <row r="232" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A232" s="11"/>
-      <c r="B232" s="14" t="s">
+      <c r="A232" s="17"/>
+      <c r="B232" s="9" t="s">
         <v>388</v>
       </c>
       <c r="C232" s="4" t="s">
@@ -12652,8 +12652,8 @@
       <c r="K232" s="6"/>
     </row>
     <row r="233" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A233" s="11"/>
-      <c r="B233" s="14" t="s">
+      <c r="A233" s="17"/>
+      <c r="B233" s="9" t="s">
         <v>389</v>
       </c>
       <c r="C233" s="4" t="s">
@@ -12683,8 +12683,8 @@
       <c r="K233" s="6"/>
     </row>
     <row r="234" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A234" s="11"/>
-      <c r="B234" s="14" t="s">
+      <c r="A234" s="17"/>
+      <c r="B234" s="9" t="s">
         <v>390</v>
       </c>
       <c r="C234" s="4" t="s">
@@ -12714,8 +12714,8 @@
       <c r="K234" s="6"/>
     </row>
     <row r="235" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A235" s="11"/>
-      <c r="B235" s="14" t="s">
+      <c r="A235" s="17"/>
+      <c r="B235" s="9" t="s">
         <v>391</v>
       </c>
       <c r="C235" s="4" t="s">
@@ -12745,8 +12745,8 @@
       <c r="K235" s="6"/>
     </row>
     <row r="236" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A236" s="11"/>
-      <c r="B236" s="14" t="s">
+      <c r="A236" s="17"/>
+      <c r="B236" s="9" t="s">
         <v>392</v>
       </c>
       <c r="C236" s="4" t="s">
@@ -12776,8 +12776,8 @@
       <c r="K236" s="6"/>
     </row>
     <row r="237" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A237" s="11"/>
-      <c r="B237" s="14" t="s">
+      <c r="A237" s="17"/>
+      <c r="B237" s="9" t="s">
         <v>393</v>
       </c>
       <c r="C237" s="4" t="s">
@@ -12807,8 +12807,8 @@
       <c r="K237" s="6"/>
     </row>
     <row r="238" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A238" s="11"/>
-      <c r="B238" s="14" t="s">
+      <c r="A238" s="17"/>
+      <c r="B238" s="9" t="s">
         <v>394</v>
       </c>
       <c r="C238" s="4" t="s">
@@ -12838,8 +12838,8 @@
       <c r="K238" s="6"/>
     </row>
     <row r="239" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A239" s="11"/>
-      <c r="B239" s="14" t="s">
+      <c r="A239" s="17"/>
+      <c r="B239" s="9" t="s">
         <v>395</v>
       </c>
       <c r="C239" s="4" t="s">
@@ -12869,8 +12869,8 @@
       <c r="K239" s="6"/>
     </row>
     <row r="240" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A240" s="11"/>
-      <c r="B240" s="14" t="s">
+      <c r="A240" s="17"/>
+      <c r="B240" s="9" t="s">
         <v>396</v>
       </c>
       <c r="C240" s="4" t="s">
@@ -12900,8 +12900,8 @@
       <c r="K240" s="6"/>
     </row>
     <row r="241" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A241" s="11"/>
-      <c r="B241" s="14" t="s">
+      <c r="A241" s="17"/>
+      <c r="B241" s="9" t="s">
         <v>397</v>
       </c>
       <c r="C241" s="4" t="s">
@@ -12931,8 +12931,8 @@
       <c r="K241" s="6"/>
     </row>
     <row r="242" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A242" s="11"/>
-      <c r="B242" s="14" t="s">
+      <c r="A242" s="17"/>
+      <c r="B242" s="9" t="s">
         <v>398</v>
       </c>
       <c r="C242" s="4" t="s">
@@ -12962,8 +12962,8 @@
       <c r="K242" s="6"/>
     </row>
     <row r="243" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A243" s="11"/>
-      <c r="B243" s="14" t="s">
+      <c r="A243" s="17"/>
+      <c r="B243" s="9" t="s">
         <v>399</v>
       </c>
       <c r="C243" s="4" t="s">
@@ -12993,8 +12993,8 @@
       <c r="K243" s="6"/>
     </row>
     <row r="244" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A244" s="11"/>
-      <c r="B244" s="14" t="s">
+      <c r="A244" s="17"/>
+      <c r="B244" s="9" t="s">
         <v>400</v>
       </c>
       <c r="C244" s="4" t="s">
@@ -13024,8 +13024,8 @@
       <c r="K244" s="6"/>
     </row>
     <row r="245" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A245" s="11"/>
-      <c r="B245" s="14" t="s">
+      <c r="A245" s="17"/>
+      <c r="B245" s="9" t="s">
         <v>401</v>
       </c>
       <c r="C245" s="4" t="s">
@@ -13055,8 +13055,8 @@
       <c r="K245" s="6"/>
     </row>
     <row r="246" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A246" s="11"/>
-      <c r="B246" s="14" t="s">
+      <c r="A246" s="17"/>
+      <c r="B246" s="9" t="s">
         <v>402</v>
       </c>
       <c r="C246" s="4" t="s">
@@ -13086,8 +13086,8 @@
       <c r="K246" s="6"/>
     </row>
     <row r="247" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A247" s="11"/>
-      <c r="B247" s="14" t="s">
+      <c r="A247" s="17"/>
+      <c r="B247" s="9" t="s">
         <v>403</v>
       </c>
       <c r="C247" s="4" t="s">
@@ -13117,8 +13117,8 @@
       <c r="K247" s="6"/>
     </row>
     <row r="248" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A248" s="11"/>
-      <c r="B248" s="14" t="s">
+      <c r="A248" s="17"/>
+      <c r="B248" s="9" t="s">
         <v>404</v>
       </c>
       <c r="C248" s="4" t="s">
@@ -13148,8 +13148,8 @@
       <c r="K248" s="6"/>
     </row>
     <row r="249" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A249" s="11"/>
-      <c r="B249" s="14" t="s">
+      <c r="A249" s="17"/>
+      <c r="B249" s="9" t="s">
         <v>405</v>
       </c>
       <c r="C249" s="4" t="s">
@@ -13179,8 +13179,8 @@
       <c r="K249" s="6"/>
     </row>
     <row r="250" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A250" s="11"/>
-      <c r="B250" s="14" t="s">
+      <c r="A250" s="17"/>
+      <c r="B250" s="9" t="s">
         <v>406</v>
       </c>
       <c r="C250" s="4" t="s">
@@ -13210,8 +13210,8 @@
       <c r="K250" s="6"/>
     </row>
     <row r="251" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A251" s="11"/>
-      <c r="B251" s="14" t="s">
+      <c r="A251" s="17"/>
+      <c r="B251" s="9" t="s">
         <v>407</v>
       </c>
       <c r="C251" s="4" t="s">
@@ -13241,8 +13241,8 @@
       <c r="K251" s="6"/>
     </row>
     <row r="252" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A252" s="11"/>
-      <c r="B252" s="14" t="s">
+      <c r="A252" s="17"/>
+      <c r="B252" s="9" t="s">
         <v>408</v>
       </c>
       <c r="C252" s="4" t="s">
@@ -13272,8 +13272,8 @@
       <c r="K252" s="6"/>
     </row>
     <row r="253" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A253" s="11"/>
-      <c r="B253" s="14" t="s">
+      <c r="A253" s="17"/>
+      <c r="B253" s="9" t="s">
         <v>409</v>
       </c>
       <c r="C253" s="4" t="s">
@@ -13303,8 +13303,8 @@
       <c r="K253" s="6"/>
     </row>
     <row r="254" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A254" s="11"/>
-      <c r="B254" s="14" t="s">
+      <c r="A254" s="17"/>
+      <c r="B254" s="9" t="s">
         <v>410</v>
       </c>
       <c r="C254" s="4" t="s">
@@ -13334,8 +13334,8 @@
       <c r="K254" s="6"/>
     </row>
     <row r="255" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A255" s="11"/>
-      <c r="B255" s="14" t="s">
+      <c r="A255" s="17"/>
+      <c r="B255" s="9" t="s">
         <v>411</v>
       </c>
       <c r="C255" s="4" t="s">
@@ -13365,8 +13365,8 @@
       <c r="K255" s="6"/>
     </row>
     <row r="256" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A256" s="11"/>
-      <c r="B256" s="14" t="s">
+      <c r="A256" s="17"/>
+      <c r="B256" s="9" t="s">
         <v>412</v>
       </c>
       <c r="C256" s="4" t="s">
@@ -13396,8 +13396,8 @@
       <c r="K256" s="6"/>
     </row>
     <row r="257" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A257" s="11"/>
-      <c r="B257" s="14" t="s">
+      <c r="A257" s="17"/>
+      <c r="B257" s="9" t="s">
         <v>413</v>
       </c>
       <c r="C257" s="4" t="s">
@@ -13427,8 +13427,8 @@
       <c r="K257" s="6"/>
     </row>
     <row r="258" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A258" s="11"/>
-      <c r="B258" s="14" t="s">
+      <c r="A258" s="17"/>
+      <c r="B258" s="9" t="s">
         <v>414</v>
       </c>
       <c r="C258" s="4" t="s">
@@ -13458,8 +13458,8 @@
       <c r="K258" s="6"/>
     </row>
     <row r="259" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A259" s="11"/>
-      <c r="B259" s="14" t="s">
+      <c r="A259" s="17"/>
+      <c r="B259" s="9" t="s">
         <v>415</v>
       </c>
       <c r="C259" s="4" t="s">
@@ -13489,8 +13489,8 @@
       <c r="K259" s="6"/>
     </row>
     <row r="260" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A260" s="11"/>
-      <c r="B260" s="14" t="s">
+      <c r="A260" s="17"/>
+      <c r="B260" s="9" t="s">
         <v>416</v>
       </c>
       <c r="C260" s="4" t="s">
@@ -13520,8 +13520,8 @@
       <c r="K260" s="6"/>
     </row>
     <row r="261" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A261" s="11"/>
-      <c r="B261" s="14" t="s">
+      <c r="A261" s="17"/>
+      <c r="B261" s="9" t="s">
         <v>417</v>
       </c>
       <c r="C261" s="4" t="s">
@@ -13551,8 +13551,8 @@
       <c r="K261" s="6"/>
     </row>
     <row r="262" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A262" s="11"/>
-      <c r="B262" s="14" t="s">
+      <c r="A262" s="17"/>
+      <c r="B262" s="9" t="s">
         <v>418</v>
       </c>
       <c r="C262" s="4" t="s">
@@ -13582,8 +13582,8 @@
       <c r="K262" s="6"/>
     </row>
     <row r="263" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A263" s="11"/>
-      <c r="B263" s="14" t="s">
+      <c r="A263" s="17"/>
+      <c r="B263" s="9" t="s">
         <v>419</v>
       </c>
       <c r="C263" s="4" t="s">
@@ -13613,8 +13613,8 @@
       <c r="K263" s="6"/>
     </row>
     <row r="264" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A264" s="11"/>
-      <c r="B264" s="14" t="s">
+      <c r="A264" s="17"/>
+      <c r="B264" s="9" t="s">
         <v>420</v>
       </c>
       <c r="C264" s="4" t="s">
@@ -13644,8 +13644,8 @@
       <c r="K264" s="6"/>
     </row>
     <row r="265" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A265" s="11"/>
-      <c r="B265" s="14" t="s">
+      <c r="A265" s="17"/>
+      <c r="B265" s="9" t="s">
         <v>421</v>
       </c>
       <c r="C265" s="4" t="s">
@@ -13675,8 +13675,8 @@
       <c r="K265" s="6"/>
     </row>
     <row r="266" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A266" s="11"/>
-      <c r="B266" s="14" t="s">
+      <c r="A266" s="17"/>
+      <c r="B266" s="9" t="s">
         <v>422</v>
       </c>
       <c r="C266" s="4" t="s">
@@ -13706,8 +13706,8 @@
       <c r="K266" s="6"/>
     </row>
     <row r="267" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A267" s="11"/>
-      <c r="B267" s="14" t="s">
+      <c r="A267" s="17"/>
+      <c r="B267" s="9" t="s">
         <v>423</v>
       </c>
       <c r="C267" s="4" t="s">
@@ -13737,8 +13737,8 @@
       <c r="K267" s="6"/>
     </row>
     <row r="268" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A268" s="11"/>
-      <c r="B268" s="14" t="s">
+      <c r="A268" s="17"/>
+      <c r="B268" s="9" t="s">
         <v>424</v>
       </c>
       <c r="C268" s="4" t="s">
@@ -13768,8 +13768,8 @@
       <c r="K268" s="6"/>
     </row>
     <row r="269" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A269" s="11"/>
-      <c r="B269" s="14" t="s">
+      <c r="A269" s="17"/>
+      <c r="B269" s="9" t="s">
         <v>425</v>
       </c>
       <c r="C269" s="4" t="s">
@@ -13799,8 +13799,8 @@
       <c r="K269" s="6"/>
     </row>
     <row r="270" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A270" s="11"/>
-      <c r="B270" s="14" t="s">
+      <c r="A270" s="17"/>
+      <c r="B270" s="9" t="s">
         <v>426</v>
       </c>
       <c r="C270" s="4" t="s">
@@ -13830,8 +13830,8 @@
       <c r="K270" s="6"/>
     </row>
     <row r="271" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A271" s="11"/>
-      <c r="B271" s="14" t="s">
+      <c r="A271" s="17"/>
+      <c r="B271" s="9" t="s">
         <v>427</v>
       </c>
       <c r="C271" s="4" t="s">
@@ -13861,8 +13861,8 @@
       <c r="K271" s="6"/>
     </row>
     <row r="272" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A272" s="11"/>
-      <c r="B272" s="14" t="s">
+      <c r="A272" s="17"/>
+      <c r="B272" s="9" t="s">
         <v>428</v>
       </c>
       <c r="C272" s="4" t="s">
@@ -13892,8 +13892,8 @@
       <c r="K272" s="6"/>
     </row>
     <row r="273" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A273" s="11"/>
-      <c r="B273" s="14" t="s">
+      <c r="A273" s="17"/>
+      <c r="B273" s="9" t="s">
         <v>429</v>
       </c>
       <c r="C273" s="4" t="s">
@@ -13923,8 +13923,8 @@
       <c r="K273" s="6"/>
     </row>
     <row r="274" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A274" s="11"/>
-      <c r="B274" s="14" t="s">
+      <c r="A274" s="17"/>
+      <c r="B274" s="9" t="s">
         <v>430</v>
       </c>
       <c r="C274" s="4" t="s">
@@ -13954,8 +13954,8 @@
       <c r="K274" s="6"/>
     </row>
     <row r="275" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A275" s="11"/>
-      <c r="B275" s="14" t="s">
+      <c r="A275" s="17"/>
+      <c r="B275" s="9" t="s">
         <v>431</v>
       </c>
       <c r="C275" s="4" t="s">
@@ -13985,8 +13985,8 @@
       <c r="K275" s="6"/>
     </row>
     <row r="276" spans="1:11" ht="15" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="11"/>
-      <c r="B276" s="14" t="s">
+      <c r="A276" s="17"/>
+      <c r="B276" s="9" t="s">
         <v>432</v>
       </c>
       <c r="C276" s="4" t="s">
@@ -14016,8 +14016,8 @@
       <c r="K276" s="6"/>
     </row>
     <row r="277" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A277" s="11"/>
-      <c r="B277" s="14" t="s">
+      <c r="A277" s="17"/>
+      <c r="B277" s="9" t="s">
         <v>433</v>
       </c>
       <c r="C277" s="4" t="s">
@@ -14047,8 +14047,8 @@
       <c r="K277" s="6"/>
     </row>
     <row r="278" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A278" s="11"/>
-      <c r="B278" s="14" t="s">
+      <c r="A278" s="17"/>
+      <c r="B278" s="9" t="s">
         <v>434</v>
       </c>
       <c r="C278" s="4" t="s">
@@ -14078,8 +14078,8 @@
       <c r="K278" s="6"/>
     </row>
     <row r="279" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A279" s="11"/>
-      <c r="B279" s="14" t="s">
+      <c r="A279" s="17"/>
+      <c r="B279" s="9" t="s">
         <v>435</v>
       </c>
       <c r="C279" s="4" t="s">
@@ -14109,8 +14109,8 @@
       <c r="K279" s="6"/>
     </row>
     <row r="280" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A280" s="11"/>
-      <c r="B280" s="14" t="s">
+      <c r="A280" s="17"/>
+      <c r="B280" s="9" t="s">
         <v>436</v>
       </c>
       <c r="C280" s="4" t="s">
@@ -14140,8 +14140,8 @@
       <c r="K280" s="6"/>
     </row>
     <row r="281" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A281" s="11"/>
-      <c r="B281" s="14" t="s">
+      <c r="A281" s="17"/>
+      <c r="B281" s="9" t="s">
         <v>437</v>
       </c>
       <c r="C281" s="4" t="s">
@@ -14171,8 +14171,8 @@
       <c r="K281" s="6"/>
     </row>
     <row r="282" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A282" s="11"/>
-      <c r="B282" s="14" t="s">
+      <c r="A282" s="17"/>
+      <c r="B282" s="9" t="s">
         <v>438</v>
       </c>
       <c r="C282" s="4" t="s">
@@ -14202,8 +14202,8 @@
       <c r="K282" s="6"/>
     </row>
     <row r="283" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A283" s="11"/>
-      <c r="B283" s="14" t="s">
+      <c r="A283" s="17"/>
+      <c r="B283" s="9" t="s">
         <v>439</v>
       </c>
       <c r="C283" s="4" t="s">
@@ -14233,8 +14233,8 @@
       <c r="K283" s="6"/>
     </row>
     <row r="284" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A284" s="11"/>
-      <c r="B284" s="14" t="s">
+      <c r="A284" s="17"/>
+      <c r="B284" s="9" t="s">
         <v>440</v>
       </c>
       <c r="C284" s="4" t="s">
@@ -14264,8 +14264,8 @@
       <c r="K284" s="6"/>
     </row>
     <row r="285" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A285" s="11"/>
-      <c r="B285" s="14" t="s">
+      <c r="A285" s="17"/>
+      <c r="B285" s="9" t="s">
         <v>441</v>
       </c>
       <c r="C285" s="4" t="s">
@@ -14295,8 +14295,8 @@
       <c r="K285" s="6"/>
     </row>
     <row r="286" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A286" s="11"/>
-      <c r="B286" s="14" t="s">
+      <c r="A286" s="17"/>
+      <c r="B286" s="9" t="s">
         <v>442</v>
       </c>
       <c r="C286" s="4" t="s">
@@ -14326,8 +14326,8 @@
       <c r="K286" s="6"/>
     </row>
     <row r="287" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A287" s="11"/>
-      <c r="B287" s="14" t="s">
+      <c r="A287" s="17"/>
+      <c r="B287" s="9" t="s">
         <v>443</v>
       </c>
       <c r="C287" s="4" t="s">
@@ -14357,8 +14357,8 @@
       <c r="K287" s="6"/>
     </row>
     <row r="288" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A288" s="11"/>
-      <c r="B288" s="14" t="s">
+      <c r="A288" s="17"/>
+      <c r="B288" s="9" t="s">
         <v>444</v>
       </c>
       <c r="C288" s="4" t="s">
@@ -14388,8 +14388,8 @@
       <c r="K288" s="6"/>
     </row>
     <row r="289" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A289" s="11"/>
-      <c r="B289" s="14" t="s">
+      <c r="A289" s="17"/>
+      <c r="B289" s="9" t="s">
         <v>445</v>
       </c>
       <c r="C289" s="4" t="s">
@@ -14419,8 +14419,8 @@
       <c r="K289" s="6"/>
     </row>
     <row r="290" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A290" s="11"/>
-      <c r="B290" s="14" t="s">
+      <c r="A290" s="17"/>
+      <c r="B290" s="9" t="s">
         <v>446</v>
       </c>
       <c r="C290" s="4" t="s">
@@ -14450,8 +14450,8 @@
       <c r="K290" s="6"/>
     </row>
     <row r="291" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A291" s="11"/>
-      <c r="B291" s="14" t="s">
+      <c r="A291" s="17"/>
+      <c r="B291" s="9" t="s">
         <v>447</v>
       </c>
       <c r="C291" s="4" t="s">
@@ -14481,8 +14481,8 @@
       <c r="K291" s="6"/>
     </row>
     <row r="292" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A292" s="11"/>
-      <c r="B292" s="14" t="s">
+      <c r="A292" s="17"/>
+      <c r="B292" s="9" t="s">
         <v>448</v>
       </c>
       <c r="C292" s="4" t="s">
@@ -14512,8 +14512,8 @@
       <c r="K292" s="6"/>
     </row>
     <row r="293" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A293" s="11"/>
-      <c r="B293" s="14" t="s">
+      <c r="A293" s="17"/>
+      <c r="B293" s="9" t="s">
         <v>449</v>
       </c>
       <c r="C293" s="4" t="s">
@@ -14543,8 +14543,8 @@
       <c r="K293" s="6"/>
     </row>
     <row r="294" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A294" s="11"/>
-      <c r="B294" s="14" t="s">
+      <c r="A294" s="17"/>
+      <c r="B294" s="9" t="s">
         <v>450</v>
       </c>
       <c r="C294" s="4" t="s">
@@ -14574,8 +14574,8 @@
       <c r="K294" s="6"/>
     </row>
     <row r="295" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A295" s="11"/>
-      <c r="B295" s="14" t="s">
+      <c r="A295" s="17"/>
+      <c r="B295" s="9" t="s">
         <v>451</v>
       </c>
       <c r="C295" s="4" t="s">
@@ -14605,8 +14605,8 @@
       <c r="K295" s="6"/>
     </row>
     <row r="296" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A296" s="11"/>
-      <c r="B296" s="14" t="s">
+      <c r="A296" s="17"/>
+      <c r="B296" s="9" t="s">
         <v>452</v>
       </c>
       <c r="C296" s="4" t="s">
@@ -14636,8 +14636,8 @@
       <c r="K296" s="6"/>
     </row>
     <row r="297" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A297" s="11"/>
-      <c r="B297" s="14" t="s">
+      <c r="A297" s="17"/>
+      <c r="B297" s="9" t="s">
         <v>453</v>
       </c>
       <c r="C297" s="4" t="s">
@@ -14667,8 +14667,8 @@
       <c r="K297" s="6"/>
     </row>
     <row r="298" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A298" s="11"/>
-      <c r="B298" s="14" t="s">
+      <c r="A298" s="17"/>
+      <c r="B298" s="9" t="s">
         <v>454</v>
       </c>
       <c r="C298" s="4" t="s">
@@ -14698,8 +14698,8 @@
       <c r="K298" s="6"/>
     </row>
     <row r="299" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A299" s="11"/>
-      <c r="B299" s="14" t="s">
+      <c r="A299" s="17"/>
+      <c r="B299" s="9" t="s">
         <v>455</v>
       </c>
       <c r="C299" s="4" t="s">
@@ -14729,8 +14729,8 @@
       <c r="K299" s="6"/>
     </row>
     <row r="300" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A300" s="11"/>
-      <c r="B300" s="14" t="s">
+      <c r="A300" s="17"/>
+      <c r="B300" s="9" t="s">
         <v>456</v>
       </c>
       <c r="C300" s="4" t="s">
@@ -14760,8 +14760,8 @@
       <c r="K300" s="6"/>
     </row>
     <row r="301" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A301" s="11"/>
-      <c r="B301" s="14" t="s">
+      <c r="A301" s="17"/>
+      <c r="B301" s="9" t="s">
         <v>457</v>
       </c>
       <c r="C301" s="4" t="s">
@@ -14791,8 +14791,8 @@
       <c r="K301" s="6"/>
     </row>
     <row r="302" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A302" s="11"/>
-      <c r="B302" s="14" t="s">
+      <c r="A302" s="17"/>
+      <c r="B302" s="9" t="s">
         <v>458</v>
       </c>
       <c r="C302" s="4" t="s">
@@ -14822,8 +14822,8 @@
       <c r="K302" s="6"/>
     </row>
     <row r="303" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A303" s="11"/>
-      <c r="B303" s="14" t="s">
+      <c r="A303" s="17"/>
+      <c r="B303" s="9" t="s">
         <v>459</v>
       </c>
       <c r="C303" s="4" t="s">
@@ -14853,8 +14853,8 @@
       <c r="K303" s="6"/>
     </row>
     <row r="304" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A304" s="11"/>
-      <c r="B304" s="14" t="s">
+      <c r="A304" s="17"/>
+      <c r="B304" s="9" t="s">
         <v>460</v>
       </c>
       <c r="C304" s="4" t="s">
@@ -14884,8 +14884,8 @@
       <c r="K304" s="6"/>
     </row>
     <row r="305" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A305" s="11"/>
-      <c r="B305" s="14" t="s">
+      <c r="A305" s="17"/>
+      <c r="B305" s="9" t="s">
         <v>461</v>
       </c>
       <c r="C305" s="4" t="s">
@@ -14915,8 +14915,8 @@
       <c r="K305" s="6"/>
     </row>
     <row r="306" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A306" s="11"/>
-      <c r="B306" s="14" t="s">
+      <c r="A306" s="17"/>
+      <c r="B306" s="9" t="s">
         <v>462</v>
       </c>
       <c r="C306" s="4" t="s">
@@ -14946,8 +14946,8 @@
       <c r="K306" s="6"/>
     </row>
     <row r="307" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A307" s="11"/>
-      <c r="B307" s="14" t="s">
+      <c r="A307" s="17"/>
+      <c r="B307" s="9" t="s">
         <v>463</v>
       </c>
       <c r="C307" s="4" t="s">
@@ -14977,8 +14977,8 @@
       <c r="K307" s="6"/>
     </row>
     <row r="308" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A308" s="11"/>
-      <c r="B308" s="14" t="s">
+      <c r="A308" s="17"/>
+      <c r="B308" s="9" t="s">
         <v>464</v>
       </c>
       <c r="C308" s="4" t="s">
@@ -15008,8 +15008,8 @@
       <c r="K308" s="6"/>
     </row>
     <row r="309" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A309" s="11"/>
-      <c r="B309" s="14" t="s">
+      <c r="A309" s="17"/>
+      <c r="B309" s="9" t="s">
         <v>465</v>
       </c>
       <c r="C309" s="4" t="s">
@@ -15039,8 +15039,8 @@
       <c r="K309" s="6"/>
     </row>
     <row r="310" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A310" s="11"/>
-      <c r="B310" s="14" t="s">
+      <c r="A310" s="17"/>
+      <c r="B310" s="9" t="s">
         <v>466</v>
       </c>
       <c r="C310" s="4" t="s">
@@ -15070,8 +15070,8 @@
       <c r="K310" s="6"/>
     </row>
     <row r="311" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A311" s="11"/>
-      <c r="B311" s="14" t="s">
+      <c r="A311" s="17"/>
+      <c r="B311" s="9" t="s">
         <v>467</v>
       </c>
       <c r="C311" s="4" t="s">
@@ -15101,8 +15101,8 @@
       <c r="K311" s="6"/>
     </row>
     <row r="312" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A312" s="11"/>
-      <c r="B312" s="14" t="s">
+      <c r="A312" s="17"/>
+      <c r="B312" s="9" t="s">
         <v>468</v>
       </c>
       <c r="C312" s="4" t="s">
@@ -15132,8 +15132,8 @@
       <c r="K312" s="6"/>
     </row>
     <row r="313" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A313" s="11"/>
-      <c r="B313" s="14" t="s">
+      <c r="A313" s="17"/>
+      <c r="B313" s="9" t="s">
         <v>469</v>
       </c>
       <c r="C313" s="4" t="s">
@@ -15163,8 +15163,8 @@
       <c r="K313" s="6"/>
     </row>
     <row r="314" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A314" s="11"/>
-      <c r="B314" s="14" t="s">
+      <c r="A314" s="17"/>
+      <c r="B314" s="9" t="s">
         <v>470</v>
       </c>
       <c r="C314" s="4" t="s">
@@ -15194,8 +15194,8 @@
       <c r="K314" s="6"/>
     </row>
     <row r="315" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A315" s="11"/>
-      <c r="B315" s="14" t="s">
+      <c r="A315" s="17"/>
+      <c r="B315" s="9" t="s">
         <v>471</v>
       </c>
       <c r="C315" s="4" t="s">
@@ -15225,8 +15225,8 @@
       <c r="K315" s="6"/>
     </row>
     <row r="316" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A316" s="11"/>
-      <c r="B316" s="14" t="s">
+      <c r="A316" s="17"/>
+      <c r="B316" s="9" t="s">
         <v>472</v>
       </c>
       <c r="C316" s="4" t="s">
@@ -15256,8 +15256,8 @@
       <c r="K316" s="6"/>
     </row>
     <row r="317" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A317" s="11"/>
-      <c r="B317" s="14" t="s">
+      <c r="A317" s="17"/>
+      <c r="B317" s="9" t="s">
         <v>473</v>
       </c>
       <c r="C317" s="4" t="s">
@@ -15287,8 +15287,8 @@
       <c r="K317" s="6"/>
     </row>
     <row r="318" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A318" s="11"/>
-      <c r="B318" s="14" t="s">
+      <c r="A318" s="17"/>
+      <c r="B318" s="9" t="s">
         <v>474</v>
       </c>
       <c r="C318" s="4" t="s">
@@ -15318,8 +15318,8 @@
       <c r="K318" s="6"/>
     </row>
     <row r="319" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A319" s="11"/>
-      <c r="B319" s="14" t="s">
+      <c r="A319" s="17"/>
+      <c r="B319" s="9" t="s">
         <v>475</v>
       </c>
       <c r="C319" s="4" t="s">
@@ -15349,8 +15349,8 @@
       <c r="K319" s="6"/>
     </row>
     <row r="320" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A320" s="11"/>
-      <c r="B320" s="14" t="s">
+      <c r="A320" s="17"/>
+      <c r="B320" s="9" t="s">
         <v>476</v>
       </c>
       <c r="C320" s="4" t="s">
@@ -15380,8 +15380,8 @@
       <c r="K320" s="6"/>
     </row>
     <row r="321" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A321" s="11"/>
-      <c r="B321" s="14" t="s">
+      <c r="A321" s="17"/>
+      <c r="B321" s="9" t="s">
         <v>477</v>
       </c>
       <c r="C321" s="4" t="s">
@@ -15411,8 +15411,8 @@
       <c r="K321" s="6"/>
     </row>
     <row r="322" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A322" s="11"/>
-      <c r="B322" s="14" t="s">
+      <c r="A322" s="17"/>
+      <c r="B322" s="9" t="s">
         <v>478</v>
       </c>
       <c r="C322" s="4" t="s">
@@ -15442,8 +15442,8 @@
       <c r="K322" s="6"/>
     </row>
     <row r="323" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A323" s="11"/>
-      <c r="B323" s="14" t="s">
+      <c r="A323" s="17"/>
+      <c r="B323" s="9" t="s">
         <v>479</v>
       </c>
       <c r="C323" s="4" t="s">
@@ -15473,8 +15473,8 @@
       <c r="K323" s="6"/>
     </row>
     <row r="324" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A324" s="11"/>
-      <c r="B324" s="14" t="s">
+      <c r="A324" s="17"/>
+      <c r="B324" s="9" t="s">
         <v>480</v>
       </c>
       <c r="C324" s="4" t="s">
@@ -15504,8 +15504,8 @@
       <c r="K324" s="6"/>
     </row>
     <row r="325" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A325" s="11"/>
-      <c r="B325" s="14" t="s">
+      <c r="A325" s="17"/>
+      <c r="B325" s="9" t="s">
         <v>481</v>
       </c>
       <c r="C325" s="4" t="s">
@@ -15535,8 +15535,8 @@
       <c r="K325" s="6"/>
     </row>
     <row r="326" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A326" s="11"/>
-      <c r="B326" s="14" t="s">
+      <c r="A326" s="17"/>
+      <c r="B326" s="9" t="s">
         <v>482</v>
       </c>
       <c r="C326" s="4" t="s">
@@ -15566,8 +15566,8 @@
       <c r="K326" s="6"/>
     </row>
     <row r="327" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A327" s="11"/>
-      <c r="B327" s="14" t="s">
+      <c r="A327" s="17"/>
+      <c r="B327" s="9" t="s">
         <v>483</v>
       </c>
       <c r="C327" s="4" t="s">
@@ -15597,8 +15597,8 @@
       <c r="K327" s="6"/>
     </row>
     <row r="328" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A328" s="11"/>
-      <c r="B328" s="14" t="s">
+      <c r="A328" s="17"/>
+      <c r="B328" s="9" t="s">
         <v>484</v>
       </c>
       <c r="C328" s="4" t="s">
@@ -15628,8 +15628,8 @@
       <c r="K328" s="6"/>
     </row>
     <row r="329" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A329" s="11"/>
-      <c r="B329" s="14" t="s">
+      <c r="A329" s="17"/>
+      <c r="B329" s="9" t="s">
         <v>485</v>
       </c>
       <c r="C329" s="4" t="s">
@@ -15659,8 +15659,8 @@
       <c r="K329" s="6"/>
     </row>
     <row r="330" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A330" s="11"/>
-      <c r="B330" s="14" t="s">
+      <c r="A330" s="17"/>
+      <c r="B330" s="9" t="s">
         <v>486</v>
       </c>
       <c r="C330" s="4" t="s">
@@ -15690,8 +15690,8 @@
       <c r="K330" s="6"/>
     </row>
     <row r="331" spans="1:11" ht="15" hidden="1" outlineLevel="2" x14ac:dyDescent="0.25">
-      <c r="A331" s="11"/>
-      <c r="B331" s="14" t="s">
+      <c r="A331" s="17"/>
+      <c r="B331" s="9" t="s">
         <v>487</v>
       </c>
       <c r="C331" s="4" t="s">
@@ -15721,8 +15721,8 @@
       <c r="K331" s="6"/>
     </row>
     <row r="332" spans="1:11" ht="15" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A332" s="11"/>
-      <c r="B332" s="14" t="s">
+      <c r="A332" s="17"/>
+      <c r="B332" s="9" t="s">
         <v>488</v>
       </c>
       <c r="C332" s="4" t="s">
@@ -15752,8 +15752,8 @@
       <c r="K332" s="6"/>
     </row>
     <row r="333" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A333" s="11"/>
-      <c r="B333" s="14" t="s">
+      <c r="A333" s="17"/>
+      <c r="B333" s="9" t="s">
         <v>489</v>
       </c>
       <c r="C333" s="4" t="s">
@@ -15786,7 +15786,7 @@
       <c r="A334" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B334" s="14" t="s">
+      <c r="B334" s="9" t="s">
         <v>113</v>
       </c>
       <c r="C334" s="4">
@@ -15819,7 +15819,7 @@
       <c r="A335" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B335" s="14" t="s">
+      <c r="B335" s="9" t="s">
         <v>114</v>
       </c>
       <c r="C335" s="4">
@@ -15852,7 +15852,7 @@
       <c r="A336" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B336" s="14" t="s">
+      <c r="B336" s="9" t="s">
         <v>115</v>
       </c>
       <c r="C336" s="4">
@@ -15882,10 +15882,10 @@
       <c r="K336" s="6"/>
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A337" s="12" t="s">
+      <c r="A337" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B337" s="14" t="s">
+      <c r="B337" s="9" t="s">
         <v>116</v>
       </c>
       <c r="C337" s="4">
@@ -15915,8 +15915,8 @@
       <c r="K337" s="6"/>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A338" s="10"/>
-      <c r="B338" s="14" t="s">
+      <c r="A338" s="15"/>
+      <c r="B338" s="9" t="s">
         <v>117</v>
       </c>
       <c r="C338" s="4">
@@ -15946,10 +15946,10 @@
       <c r="K338" s="6"/>
     </row>
     <row r="339" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A339" s="12" t="s">
+      <c r="A339" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B339" s="14" t="s">
+      <c r="B339" s="9" t="s">
         <v>490</v>
       </c>
       <c r="C339" s="4">
@@ -15979,8 +15979,8 @@
       <c r="K339" s="6"/>
     </row>
     <row r="340" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="13"/>
-      <c r="B340" s="14" t="s">
+      <c r="A340" s="14"/>
+      <c r="B340" s="9" t="s">
         <v>491</v>
       </c>
       <c r="C340" s="4">
@@ -16010,8 +16010,8 @@
       <c r="K340" s="6"/>
     </row>
     <row r="341" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="13"/>
-      <c r="B341" s="14" t="s">
+      <c r="A341" s="14"/>
+      <c r="B341" s="9" t="s">
         <v>492</v>
       </c>
       <c r="C341" s="4">
@@ -16041,8 +16041,8 @@
       <c r="K341" s="6"/>
     </row>
     <row r="342" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="13"/>
-      <c r="B342" s="14" t="s">
+      <c r="A342" s="14"/>
+      <c r="B342" s="9" t="s">
         <v>493</v>
       </c>
       <c r="C342" s="4">
@@ -16072,8 +16072,8 @@
       <c r="K342" s="6"/>
     </row>
     <row r="343" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="13"/>
-      <c r="B343" s="14" t="s">
+      <c r="A343" s="14"/>
+      <c r="B343" s="9" t="s">
         <v>494</v>
       </c>
       <c r="C343" s="4">
@@ -16103,8 +16103,8 @@
       <c r="K343" s="6"/>
     </row>
     <row r="344" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A344" s="13"/>
-      <c r="B344" s="14" t="s">
+      <c r="A344" s="14"/>
+      <c r="B344" s="9" t="s">
         <v>495</v>
       </c>
       <c r="C344" s="4">
@@ -16134,8 +16134,8 @@
       <c r="K344" s="6"/>
     </row>
     <row r="345" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A345" s="13"/>
-      <c r="B345" s="14" t="s">
+      <c r="A345" s="14"/>
+      <c r="B345" s="9" t="s">
         <v>496</v>
       </c>
       <c r="C345" s="4">
@@ -16165,8 +16165,8 @@
       <c r="K345" s="6"/>
     </row>
     <row r="346" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A346" s="13"/>
-      <c r="B346" s="14" t="s">
+      <c r="A346" s="14"/>
+      <c r="B346" s="9" t="s">
         <v>497</v>
       </c>
       <c r="C346" s="4">
@@ -16196,8 +16196,8 @@
       <c r="K346" s="6"/>
     </row>
     <row r="347" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="13"/>
-      <c r="B347" s="14" t="s">
+      <c r="A347" s="14"/>
+      <c r="B347" s="9" t="s">
         <v>498</v>
       </c>
       <c r="C347" s="4">
@@ -16227,8 +16227,8 @@
       <c r="K347" s="6"/>
     </row>
     <row r="348" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A348" s="13"/>
-      <c r="B348" s="14" t="s">
+      <c r="A348" s="14"/>
+      <c r="B348" s="9" t="s">
         <v>499</v>
       </c>
       <c r="C348" s="4">
@@ -16258,8 +16258,8 @@
       <c r="K348" s="6"/>
     </row>
     <row r="349" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A349" s="13"/>
-      <c r="B349" s="14" t="s">
+      <c r="A349" s="14"/>
+      <c r="B349" s="9" t="s">
         <v>500</v>
       </c>
       <c r="C349" s="4">
@@ -16289,8 +16289,8 @@
       <c r="K349" s="6"/>
     </row>
     <row r="350" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="13"/>
-      <c r="B350" s="14" t="s">
+      <c r="A350" s="14"/>
+      <c r="B350" s="9" t="s">
         <v>501</v>
       </c>
       <c r="C350" s="4">
@@ -16320,8 +16320,8 @@
       <c r="K350" s="6"/>
     </row>
     <row r="351" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="13"/>
-      <c r="B351" s="14" t="s">
+      <c r="A351" s="14"/>
+      <c r="B351" s="9" t="s">
         <v>502</v>
       </c>
       <c r="C351" s="4">
@@ -16351,8 +16351,8 @@
       <c r="K351" s="6"/>
     </row>
     <row r="352" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="13"/>
-      <c r="B352" s="14" t="s">
+      <c r="A352" s="14"/>
+      <c r="B352" s="9" t="s">
         <v>503</v>
       </c>
       <c r="C352" s="4">
@@ -16382,8 +16382,8 @@
       <c r="K352" s="6"/>
     </row>
     <row r="353" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A353" s="13"/>
-      <c r="B353" s="14" t="s">
+      <c r="A353" s="14"/>
+      <c r="B353" s="9" t="s">
         <v>504</v>
       </c>
       <c r="C353" s="4">
@@ -16413,8 +16413,8 @@
       <c r="K353" s="6"/>
     </row>
     <row r="354" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A354" s="10"/>
-      <c r="B354" s="14" t="s">
+      <c r="A354" s="15"/>
+      <c r="B354" s="9" t="s">
         <v>505</v>
       </c>
       <c r="C354" s="4">
@@ -16444,10 +16444,10 @@
       <c r="K354" s="6"/>
     </row>
     <row r="355" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A355" s="11" t="s">
+      <c r="A355" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B355" s="17" t="s">
+      <c r="B355" s="12" t="s">
         <v>202</v>
       </c>
       <c r="C355" s="4">
@@ -16477,8 +16477,8 @@
       <c r="K355" s="6"/>
     </row>
     <row r="356" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A356" s="11"/>
-      <c r="B356" s="17" t="s">
+      <c r="A356" s="17"/>
+      <c r="B356" s="12" t="s">
         <v>203</v>
       </c>
       <c r="C356" s="4">
@@ -16508,8 +16508,8 @@
       <c r="K356" s="6"/>
     </row>
     <row r="357" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A357" s="11"/>
-      <c r="B357" s="17" t="s">
+      <c r="A357" s="17"/>
+      <c r="B357" s="12" t="s">
         <v>204</v>
       </c>
       <c r="C357" s="4">
@@ -16539,8 +16539,8 @@
       <c r="K357" s="6"/>
     </row>
     <row r="358" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A358" s="11"/>
-      <c r="B358" s="17" t="s">
+      <c r="A358" s="17"/>
+      <c r="B358" s="12" t="s">
         <v>205</v>
       </c>
       <c r="C358" s="4">
@@ -16570,8 +16570,8 @@
       <c r="K358" s="6"/>
     </row>
     <row r="359" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A359" s="11"/>
-      <c r="B359" s="17" t="s">
+      <c r="A359" s="17"/>
+      <c r="B359" s="12" t="s">
         <v>206</v>
       </c>
       <c r="C359" s="4">
@@ -16601,8 +16601,8 @@
       <c r="K359" s="6"/>
     </row>
     <row r="360" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A360" s="11"/>
-      <c r="B360" s="17" t="s">
+      <c r="A360" s="17"/>
+      <c r="B360" s="12" t="s">
         <v>207</v>
       </c>
       <c r="C360" s="4">
@@ -16632,8 +16632,8 @@
       <c r="K360" s="6"/>
     </row>
     <row r="361" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A361" s="11"/>
-      <c r="B361" s="17" t="s">
+      <c r="A361" s="17"/>
+      <c r="B361" s="12" t="s">
         <v>208</v>
       </c>
       <c r="C361" s="4">
@@ -16663,8 +16663,8 @@
       <c r="K361" s="6"/>
     </row>
     <row r="362" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A362" s="11"/>
-      <c r="B362" s="17" t="s">
+      <c r="A362" s="17"/>
+      <c r="B362" s="12" t="s">
         <v>209</v>
       </c>
       <c r="C362" s="4">
@@ -16694,8 +16694,8 @@
       <c r="K362" s="6"/>
     </row>
     <row r="363" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A363" s="11"/>
-      <c r="B363" s="17" t="s">
+      <c r="A363" s="17"/>
+      <c r="B363" s="12" t="s">
         <v>210</v>
       </c>
       <c r="C363" s="4">
@@ -16725,8 +16725,8 @@
       <c r="K363" s="6"/>
     </row>
     <row r="364" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A364" s="11"/>
-      <c r="B364" s="17" t="s">
+      <c r="A364" s="17"/>
+      <c r="B364" s="12" t="s">
         <v>211</v>
       </c>
       <c r="C364" s="4">
@@ -16756,8 +16756,8 @@
       <c r="K364" s="6"/>
     </row>
     <row r="365" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A365" s="11"/>
-      <c r="B365" s="17" t="s">
+      <c r="A365" s="17"/>
+      <c r="B365" s="12" t="s">
         <v>212</v>
       </c>
       <c r="C365" s="4">
@@ -16787,8 +16787,8 @@
       <c r="K365" s="6"/>
     </row>
     <row r="366" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A366" s="11"/>
-      <c r="B366" s="17" t="s">
+      <c r="A366" s="17"/>
+      <c r="B366" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C366" s="4">
@@ -16818,8 +16818,8 @@
       <c r="K366" s="6"/>
     </row>
     <row r="367" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A367" s="11"/>
-      <c r="B367" s="17" t="s">
+      <c r="A367" s="17"/>
+      <c r="B367" s="12" t="s">
         <v>214</v>
       </c>
       <c r="C367" s="4">
@@ -16849,8 +16849,8 @@
       <c r="K367" s="6"/>
     </row>
     <row r="368" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A368" s="11"/>
-      <c r="B368" s="17" t="s">
+      <c r="A368" s="17"/>
+      <c r="B368" s="12" t="s">
         <v>215</v>
       </c>
       <c r="C368" s="4">
@@ -16880,8 +16880,8 @@
       <c r="K368" s="6"/>
     </row>
     <row r="369" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A369" s="11"/>
-      <c r="B369" s="17" t="s">
+      <c r="A369" s="17"/>
+      <c r="B369" s="12" t="s">
         <v>216</v>
       </c>
       <c r="C369" s="4">
@@ -16911,8 +16911,8 @@
       <c r="K369" s="6"/>
     </row>
     <row r="370" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A370" s="11"/>
-      <c r="B370" s="17" t="s">
+      <c r="A370" s="17"/>
+      <c r="B370" s="12" t="s">
         <v>217</v>
       </c>
       <c r="C370" s="4">
@@ -16945,7 +16945,7 @@
       <c r="A371" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B371" s="14" t="s">
+      <c r="B371" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C371" s="4">
@@ -16975,10 +16975,10 @@
       <c r="K371" s="6"/>
     </row>
     <row r="372" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A372" s="11" t="s">
+      <c r="A372" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B372" s="17" t="s">
+      <c r="B372" s="12" t="s">
         <v>218</v>
       </c>
       <c r="C372" s="4">
@@ -17008,8 +17008,8 @@
       <c r="K372" s="6"/>
     </row>
     <row r="373" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A373" s="11"/>
-      <c r="B373" s="17" t="s">
+      <c r="A373" s="17"/>
+      <c r="B373" s="12" t="s">
         <v>219</v>
       </c>
       <c r="C373" s="4">
@@ -17039,8 +17039,8 @@
       <c r="K373" s="6"/>
     </row>
     <row r="374" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A374" s="11"/>
-      <c r="B374" s="17" t="s">
+      <c r="A374" s="17"/>
+      <c r="B374" s="12" t="s">
         <v>220</v>
       </c>
       <c r="C374" s="4">
@@ -17070,8 +17070,8 @@
       <c r="K374" s="6"/>
     </row>
     <row r="375" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A375" s="11"/>
-      <c r="B375" s="17" t="s">
+      <c r="A375" s="17"/>
+      <c r="B375" s="12" t="s">
         <v>221</v>
       </c>
       <c r="C375" s="4">
@@ -17101,8 +17101,8 @@
       <c r="K375" s="6"/>
     </row>
     <row r="376" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A376" s="11"/>
-      <c r="B376" s="17" t="s">
+      <c r="A376" s="17"/>
+      <c r="B376" s="12" t="s">
         <v>222</v>
       </c>
       <c r="C376" s="4">
@@ -17132,8 +17132,8 @@
       <c r="K376" s="6"/>
     </row>
     <row r="377" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A377" s="11"/>
-      <c r="B377" s="17" t="s">
+      <c r="A377" s="17"/>
+      <c r="B377" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C377" s="4">
@@ -17163,8 +17163,8 @@
       <c r="K377" s="6"/>
     </row>
     <row r="378" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A378" s="11"/>
-      <c r="B378" s="17" t="s">
+      <c r="A378" s="17"/>
+      <c r="B378" s="12" t="s">
         <v>224</v>
       </c>
       <c r="C378" s="4">
@@ -17194,8 +17194,8 @@
       <c r="K378" s="6"/>
     </row>
     <row r="379" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A379" s="11"/>
-      <c r="B379" s="17" t="s">
+      <c r="A379" s="17"/>
+      <c r="B379" s="12" t="s">
         <v>225</v>
       </c>
       <c r="C379" s="4">
@@ -17225,8 +17225,8 @@
       <c r="K379" s="6"/>
     </row>
     <row r="380" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A380" s="11"/>
-      <c r="B380" s="17" t="s">
+      <c r="A380" s="17"/>
+      <c r="B380" s="12" t="s">
         <v>226</v>
       </c>
       <c r="C380" s="4">
@@ -17256,8 +17256,8 @@
       <c r="K380" s="6"/>
     </row>
     <row r="381" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A381" s="11"/>
-      <c r="B381" s="17" t="s">
+      <c r="A381" s="17"/>
+      <c r="B381" s="12" t="s">
         <v>227</v>
       </c>
       <c r="C381" s="4">
@@ -17287,8 +17287,8 @@
       <c r="K381" s="6"/>
     </row>
     <row r="382" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A382" s="11"/>
-      <c r="B382" s="17" t="s">
+      <c r="A382" s="17"/>
+      <c r="B382" s="12" t="s">
         <v>228</v>
       </c>
       <c r="C382" s="4">
@@ -17318,8 +17318,8 @@
       <c r="K382" s="6"/>
     </row>
     <row r="383" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A383" s="11"/>
-      <c r="B383" s="17" t="s">
+      <c r="A383" s="17"/>
+      <c r="B383" s="12" t="s">
         <v>229</v>
       </c>
       <c r="C383" s="4">
@@ -17349,8 +17349,8 @@
       <c r="K383" s="6"/>
     </row>
     <row r="384" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A384" s="11"/>
-      <c r="B384" s="17" t="s">
+      <c r="A384" s="17"/>
+      <c r="B384" s="12" t="s">
         <v>230</v>
       </c>
       <c r="C384" s="4">
@@ -17380,8 +17380,8 @@
       <c r="K384" s="6"/>
     </row>
     <row r="385" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A385" s="11"/>
-      <c r="B385" s="17" t="s">
+      <c r="A385" s="17"/>
+      <c r="B385" s="12" t="s">
         <v>231</v>
       </c>
       <c r="C385" s="4">
@@ -17411,8 +17411,8 @@
       <c r="K385" s="6"/>
     </row>
     <row r="386" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A386" s="11"/>
-      <c r="B386" s="17" t="s">
+      <c r="A386" s="17"/>
+      <c r="B386" s="12" t="s">
         <v>232</v>
       </c>
       <c r="C386" s="4">
@@ -17442,8 +17442,8 @@
       <c r="K386" s="6"/>
     </row>
     <row r="387" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A387" s="11"/>
-      <c r="B387" s="17" t="s">
+      <c r="A387" s="17"/>
+      <c r="B387" s="12" t="s">
         <v>233</v>
       </c>
       <c r="C387" s="4">
@@ -17473,10 +17473,10 @@
       <c r="K387" s="6"/>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A388" s="11" t="s">
+      <c r="A388" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B388" s="14" t="s">
+      <c r="B388" s="9" t="s">
         <v>119</v>
       </c>
       <c r="C388" s="4">
@@ -17506,8 +17506,8 @@
       <c r="K388" s="6"/>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A389" s="11"/>
-      <c r="B389" s="14" t="s">
+      <c r="A389" s="17"/>
+      <c r="B389" s="9" t="s">
         <v>120</v>
       </c>
       <c r="C389" s="4">
@@ -17540,7 +17540,7 @@
       <c r="A390" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B390" s="14" t="s">
+      <c r="B390" s="9" t="s">
         <v>121</v>
       </c>
       <c r="C390" s="4">
@@ -17570,10 +17570,10 @@
       <c r="K390" s="6"/>
     </row>
     <row r="391" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A391" s="11" t="s">
+      <c r="A391" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B391" s="17" t="s">
+      <c r="B391" s="12" t="s">
         <v>122</v>
       </c>
       <c r="C391" s="4">
@@ -17603,8 +17603,8 @@
       <c r="K391" s="6"/>
     </row>
     <row r="392" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A392" s="11"/>
-      <c r="B392" s="17" t="s">
+      <c r="A392" s="17"/>
+      <c r="B392" s="12" t="s">
         <v>123</v>
       </c>
       <c r="C392" s="4">
@@ -17634,8 +17634,8 @@
       <c r="K392" s="6"/>
     </row>
     <row r="393" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A393" s="11"/>
-      <c r="B393" s="17" t="s">
+      <c r="A393" s="17"/>
+      <c r="B393" s="12" t="s">
         <v>124</v>
       </c>
       <c r="C393" s="4">
@@ -17665,8 +17665,8 @@
       <c r="K393" s="6"/>
     </row>
     <row r="394" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A394" s="11"/>
-      <c r="B394" s="17" t="s">
+      <c r="A394" s="17"/>
+      <c r="B394" s="12" t="s">
         <v>125</v>
       </c>
       <c r="C394" s="4">
@@ -17696,8 +17696,8 @@
       <c r="K394" s="6"/>
     </row>
     <row r="395" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A395" s="11"/>
-      <c r="B395" s="17" t="s">
+      <c r="A395" s="17"/>
+      <c r="B395" s="12" t="s">
         <v>126</v>
       </c>
       <c r="C395" s="4">
@@ -17727,8 +17727,8 @@
       <c r="K395" s="6"/>
     </row>
     <row r="396" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A396" s="11"/>
-      <c r="B396" s="17" t="s">
+      <c r="A396" s="17"/>
+      <c r="B396" s="12" t="s">
         <v>127</v>
       </c>
       <c r="C396" s="4">
@@ -17758,8 +17758,8 @@
       <c r="K396" s="6"/>
     </row>
     <row r="397" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A397" s="11"/>
-      <c r="B397" s="17" t="s">
+      <c r="A397" s="17"/>
+      <c r="B397" s="12" t="s">
         <v>128</v>
       </c>
       <c r="C397" s="4">
@@ -17789,8 +17789,8 @@
       <c r="K397" s="6"/>
     </row>
     <row r="398" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A398" s="11"/>
-      <c r="B398" s="17" t="s">
+      <c r="A398" s="17"/>
+      <c r="B398" s="12" t="s">
         <v>129</v>
       </c>
       <c r="C398" s="4">
@@ -17820,8 +17820,8 @@
       <c r="K398" s="6"/>
     </row>
     <row r="399" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A399" s="11"/>
-      <c r="B399" s="17" t="s">
+      <c r="A399" s="17"/>
+      <c r="B399" s="12" t="s">
         <v>130</v>
       </c>
       <c r="C399" s="4">
@@ -17851,8 +17851,8 @@
       <c r="K399" s="6"/>
     </row>
     <row r="400" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A400" s="11"/>
-      <c r="B400" s="17" t="s">
+      <c r="A400" s="17"/>
+      <c r="B400" s="12" t="s">
         <v>131</v>
       </c>
       <c r="C400" s="4">
@@ -17882,8 +17882,8 @@
       <c r="K400" s="6"/>
     </row>
     <row r="401" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A401" s="11"/>
-      <c r="B401" s="17" t="s">
+      <c r="A401" s="17"/>
+      <c r="B401" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C401" s="4">
@@ -17913,8 +17913,8 @@
       <c r="K401" s="6"/>
     </row>
     <row r="402" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A402" s="11"/>
-      <c r="B402" s="17" t="s">
+      <c r="A402" s="17"/>
+      <c r="B402" s="12" t="s">
         <v>133</v>
       </c>
       <c r="C402" s="4">
@@ -17944,8 +17944,8 @@
       <c r="K402" s="6"/>
     </row>
     <row r="403" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A403" s="11"/>
-      <c r="B403" s="17" t="s">
+      <c r="A403" s="17"/>
+      <c r="B403" s="12" t="s">
         <v>134</v>
       </c>
       <c r="C403" s="4">
@@ -17975,8 +17975,8 @@
       <c r="K403" s="6"/>
     </row>
     <row r="404" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A404" s="11"/>
-      <c r="B404" s="17" t="s">
+      <c r="A404" s="17"/>
+      <c r="B404" s="12" t="s">
         <v>135</v>
       </c>
       <c r="C404" s="4">
@@ -18006,8 +18006,8 @@
       <c r="K404" s="6"/>
     </row>
     <row r="405" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A405" s="11"/>
-      <c r="B405" s="17" t="s">
+      <c r="A405" s="17"/>
+      <c r="B405" s="12" t="s">
         <v>136</v>
       </c>
       <c r="C405" s="4">
@@ -18037,8 +18037,8 @@
       <c r="K405" s="6"/>
     </row>
     <row r="406" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A406" s="11"/>
-      <c r="B406" s="17" t="s">
+      <c r="A406" s="17"/>
+      <c r="B406" s="12" t="s">
         <v>137</v>
       </c>
       <c r="C406" s="4">
@@ -18068,10 +18068,10 @@
       <c r="K406" s="6"/>
     </row>
     <row r="407" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A407" s="11" t="s">
+      <c r="A407" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B407" s="17" t="s">
+      <c r="B407" s="12" t="s">
         <v>138</v>
       </c>
       <c r="C407" s="4">
@@ -18101,8 +18101,8 @@
       <c r="K407" s="6"/>
     </row>
     <row r="408" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A408" s="11"/>
-      <c r="B408" s="17" t="s">
+      <c r="A408" s="17"/>
+      <c r="B408" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C408" s="4">
@@ -18132,8 +18132,8 @@
       <c r="K408" s="6"/>
     </row>
     <row r="409" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A409" s="11"/>
-      <c r="B409" s="17" t="s">
+      <c r="A409" s="17"/>
+      <c r="B409" s="12" t="s">
         <v>140</v>
       </c>
       <c r="C409" s="4">
@@ -18163,8 +18163,8 @@
       <c r="K409" s="6"/>
     </row>
     <row r="410" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A410" s="11"/>
-      <c r="B410" s="17" t="s">
+      <c r="A410" s="17"/>
+      <c r="B410" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C410" s="4">
@@ -18194,8 +18194,8 @@
       <c r="K410" s="6"/>
     </row>
     <row r="411" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A411" s="11"/>
-      <c r="B411" s="17" t="s">
+      <c r="A411" s="17"/>
+      <c r="B411" s="12" t="s">
         <v>142</v>
       </c>
       <c r="C411" s="4">
@@ -18225,8 +18225,8 @@
       <c r="K411" s="6"/>
     </row>
     <row r="412" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A412" s="11"/>
-      <c r="B412" s="17" t="s">
+      <c r="A412" s="17"/>
+      <c r="B412" s="12" t="s">
         <v>143</v>
       </c>
       <c r="C412" s="4">
@@ -18256,8 +18256,8 @@
       <c r="K412" s="6"/>
     </row>
     <row r="413" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A413" s="11"/>
-      <c r="B413" s="17" t="s">
+      <c r="A413" s="17"/>
+      <c r="B413" s="12" t="s">
         <v>144</v>
       </c>
       <c r="C413" s="4">
@@ -18287,8 +18287,8 @@
       <c r="K413" s="6"/>
     </row>
     <row r="414" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A414" s="11"/>
-      <c r="B414" s="17" t="s">
+      <c r="A414" s="17"/>
+      <c r="B414" s="12" t="s">
         <v>145</v>
       </c>
       <c r="C414" s="4">
@@ -18318,8 +18318,8 @@
       <c r="K414" s="6"/>
     </row>
     <row r="415" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A415" s="11"/>
-      <c r="B415" s="17" t="s">
+      <c r="A415" s="17"/>
+      <c r="B415" s="12" t="s">
         <v>146</v>
       </c>
       <c r="C415" s="4">
@@ -18349,8 +18349,8 @@
       <c r="K415" s="6"/>
     </row>
     <row r="416" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A416" s="11"/>
-      <c r="B416" s="17" t="s">
+      <c r="A416" s="17"/>
+      <c r="B416" s="12" t="s">
         <v>147</v>
       </c>
       <c r="C416" s="4">
@@ -18380,8 +18380,8 @@
       <c r="K416" s="6"/>
     </row>
     <row r="417" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A417" s="11"/>
-      <c r="B417" s="17" t="s">
+      <c r="A417" s="17"/>
+      <c r="B417" s="12" t="s">
         <v>148</v>
       </c>
       <c r="C417" s="4">
@@ -18411,8 +18411,8 @@
       <c r="K417" s="6"/>
     </row>
     <row r="418" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A418" s="11"/>
-      <c r="B418" s="17" t="s">
+      <c r="A418" s="17"/>
+      <c r="B418" s="12" t="s">
         <v>149</v>
       </c>
       <c r="C418" s="4">
@@ -18442,8 +18442,8 @@
       <c r="K418" s="6"/>
     </row>
     <row r="419" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A419" s="11"/>
-      <c r="B419" s="17" t="s">
+      <c r="A419" s="17"/>
+      <c r="B419" s="12" t="s">
         <v>150</v>
       </c>
       <c r="C419" s="4">
@@ -18473,8 +18473,8 @@
       <c r="K419" s="6"/>
     </row>
     <row r="420" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A420" s="11"/>
-      <c r="B420" s="17" t="s">
+      <c r="A420" s="17"/>
+      <c r="B420" s="12" t="s">
         <v>151</v>
       </c>
       <c r="C420" s="4">
@@ -18504,8 +18504,8 @@
       <c r="K420" s="6"/>
     </row>
     <row r="421" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A421" s="11"/>
-      <c r="B421" s="17" t="s">
+      <c r="A421" s="17"/>
+      <c r="B421" s="12" t="s">
         <v>152</v>
       </c>
       <c r="C421" s="4">
@@ -18535,8 +18535,8 @@
       <c r="K421" s="6"/>
     </row>
     <row r="422" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A422" s="11"/>
-      <c r="B422" s="17" t="s">
+      <c r="A422" s="17"/>
+      <c r="B422" s="12" t="s">
         <v>153</v>
       </c>
       <c r="C422" s="4">
@@ -18566,10 +18566,10 @@
       <c r="K422" s="6"/>
     </row>
     <row r="423" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A423" s="11" t="s">
+      <c r="A423" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B423" s="17" t="s">
+      <c r="B423" s="12" t="s">
         <v>154</v>
       </c>
       <c r="C423" s="4">
@@ -18599,8 +18599,8 @@
       <c r="K423" s="6"/>
     </row>
     <row r="424" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A424" s="11"/>
-      <c r="B424" s="17" t="s">
+      <c r="A424" s="17"/>
+      <c r="B424" s="12" t="s">
         <v>155</v>
       </c>
       <c r="C424" s="4">
@@ -18630,8 +18630,8 @@
       <c r="K424" s="6"/>
     </row>
     <row r="425" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A425" s="11"/>
-      <c r="B425" s="17" t="s">
+      <c r="A425" s="17"/>
+      <c r="B425" s="12" t="s">
         <v>156</v>
       </c>
       <c r="C425" s="4">
@@ -18661,8 +18661,8 @@
       <c r="K425" s="6"/>
     </row>
     <row r="426" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A426" s="11"/>
-      <c r="B426" s="17" t="s">
+      <c r="A426" s="17"/>
+      <c r="B426" s="12" t="s">
         <v>157</v>
       </c>
       <c r="C426" s="4">
@@ -18692,8 +18692,8 @@
       <c r="K426" s="6"/>
     </row>
     <row r="427" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A427" s="11"/>
-      <c r="B427" s="17" t="s">
+      <c r="A427" s="17"/>
+      <c r="B427" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C427" s="4">
@@ -18723,8 +18723,8 @@
       <c r="K427" s="6"/>
     </row>
     <row r="428" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A428" s="11"/>
-      <c r="B428" s="17" t="s">
+      <c r="A428" s="17"/>
+      <c r="B428" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C428" s="4">
@@ -18754,8 +18754,8 @@
       <c r="K428" s="6"/>
     </row>
     <row r="429" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A429" s="11"/>
-      <c r="B429" s="17" t="s">
+      <c r="A429" s="17"/>
+      <c r="B429" s="12" t="s">
         <v>160</v>
       </c>
       <c r="C429" s="4">
@@ -18785,8 +18785,8 @@
       <c r="K429" s="6"/>
     </row>
     <row r="430" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A430" s="11"/>
-      <c r="B430" s="17" t="s">
+      <c r="A430" s="17"/>
+      <c r="B430" s="12" t="s">
         <v>161</v>
       </c>
       <c r="C430" s="4">
@@ -18816,8 +18816,8 @@
       <c r="K430" s="6"/>
     </row>
     <row r="431" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A431" s="11"/>
-      <c r="B431" s="17" t="s">
+      <c r="A431" s="17"/>
+      <c r="B431" s="12" t="s">
         <v>162</v>
       </c>
       <c r="C431" s="4">
@@ -18847,8 +18847,8 @@
       <c r="K431" s="6"/>
     </row>
     <row r="432" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A432" s="11"/>
-      <c r="B432" s="17" t="s">
+      <c r="A432" s="17"/>
+      <c r="B432" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C432" s="4">
@@ -18878,8 +18878,8 @@
       <c r="K432" s="6"/>
     </row>
     <row r="433" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A433" s="11"/>
-      <c r="B433" s="17" t="s">
+      <c r="A433" s="17"/>
+      <c r="B433" s="12" t="s">
         <v>164</v>
       </c>
       <c r="C433" s="4">
@@ -18909,8 +18909,8 @@
       <c r="K433" s="6"/>
     </row>
     <row r="434" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A434" s="11"/>
-      <c r="B434" s="17" t="s">
+      <c r="A434" s="17"/>
+      <c r="B434" s="12" t="s">
         <v>165</v>
       </c>
       <c r="C434" s="4">
@@ -18940,8 +18940,8 @@
       <c r="K434" s="6"/>
     </row>
     <row r="435" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A435" s="11"/>
-      <c r="B435" s="17" t="s">
+      <c r="A435" s="17"/>
+      <c r="B435" s="12" t="s">
         <v>166</v>
       </c>
       <c r="C435" s="4">
@@ -18971,8 +18971,8 @@
       <c r="K435" s="6"/>
     </row>
     <row r="436" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A436" s="11"/>
-      <c r="B436" s="17" t="s">
+      <c r="A436" s="17"/>
+      <c r="B436" s="12" t="s">
         <v>167</v>
       </c>
       <c r="C436" s="4">
@@ -19002,8 +19002,8 @@
       <c r="K436" s="6"/>
     </row>
     <row r="437" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A437" s="11"/>
-      <c r="B437" s="17" t="s">
+      <c r="A437" s="17"/>
+      <c r="B437" s="12" t="s">
         <v>168</v>
       </c>
       <c r="C437" s="4">
@@ -19033,8 +19033,8 @@
       <c r="K437" s="6"/>
     </row>
     <row r="438" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A438" s="11"/>
-      <c r="B438" s="17" t="s">
+      <c r="A438" s="17"/>
+      <c r="B438" s="12" t="s">
         <v>169</v>
       </c>
       <c r="C438" s="4">
@@ -19064,10 +19064,10 @@
       <c r="K438" s="6"/>
     </row>
     <row r="439" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A439" s="11" t="s">
+      <c r="A439" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B439" s="17" t="s">
+      <c r="B439" s="12" t="s">
         <v>170</v>
       </c>
       <c r="C439" s="4">
@@ -19097,8 +19097,8 @@
       <c r="K439" s="6"/>
     </row>
     <row r="440" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A440" s="11"/>
-      <c r="B440" s="17" t="s">
+      <c r="A440" s="17"/>
+      <c r="B440" s="12" t="s">
         <v>171</v>
       </c>
       <c r="C440" s="4">
@@ -19128,8 +19128,8 @@
       <c r="K440" s="6"/>
     </row>
     <row r="441" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A441" s="11"/>
-      <c r="B441" s="17" t="s">
+      <c r="A441" s="17"/>
+      <c r="B441" s="12" t="s">
         <v>172</v>
       </c>
       <c r="C441" s="4">
@@ -19159,8 +19159,8 @@
       <c r="K441" s="6"/>
     </row>
     <row r="442" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A442" s="11"/>
-      <c r="B442" s="17" t="s">
+      <c r="A442" s="17"/>
+      <c r="B442" s="12" t="s">
         <v>173</v>
       </c>
       <c r="C442" s="4">
@@ -19190,8 +19190,8 @@
       <c r="K442" s="6"/>
     </row>
     <row r="443" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A443" s="11"/>
-      <c r="B443" s="17" t="s">
+      <c r="A443" s="17"/>
+      <c r="B443" s="12" t="s">
         <v>174</v>
       </c>
       <c r="C443" s="4">
@@ -19221,8 +19221,8 @@
       <c r="K443" s="6"/>
     </row>
     <row r="444" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A444" s="11"/>
-      <c r="B444" s="17" t="s">
+      <c r="A444" s="17"/>
+      <c r="B444" s="12" t="s">
         <v>175</v>
       </c>
       <c r="C444" s="4">
@@ -19252,8 +19252,8 @@
       <c r="K444" s="6"/>
     </row>
     <row r="445" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A445" s="11"/>
-      <c r="B445" s="17" t="s">
+      <c r="A445" s="17"/>
+      <c r="B445" s="12" t="s">
         <v>176</v>
       </c>
       <c r="C445" s="4">
@@ -19283,8 +19283,8 @@
       <c r="K445" s="6"/>
     </row>
     <row r="446" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A446" s="11"/>
-      <c r="B446" s="17" t="s">
+      <c r="A446" s="17"/>
+      <c r="B446" s="12" t="s">
         <v>177</v>
       </c>
       <c r="C446" s="4">
@@ -19314,8 +19314,8 @@
       <c r="K446" s="6"/>
     </row>
     <row r="447" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A447" s="11"/>
-      <c r="B447" s="17" t="s">
+      <c r="A447" s="17"/>
+      <c r="B447" s="12" t="s">
         <v>178</v>
       </c>
       <c r="C447" s="4">
@@ -19345,8 +19345,8 @@
       <c r="K447" s="6"/>
     </row>
     <row r="448" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A448" s="11"/>
-      <c r="B448" s="17" t="s">
+      <c r="A448" s="17"/>
+      <c r="B448" s="12" t="s">
         <v>179</v>
       </c>
       <c r="C448" s="4">
@@ -19376,8 +19376,8 @@
       <c r="K448" s="6"/>
     </row>
     <row r="449" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A449" s="11"/>
-      <c r="B449" s="17" t="s">
+      <c r="A449" s="17"/>
+      <c r="B449" s="12" t="s">
         <v>180</v>
       </c>
       <c r="C449" s="4">
@@ -19407,8 +19407,8 @@
       <c r="K449" s="6"/>
     </row>
     <row r="450" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A450" s="11"/>
-      <c r="B450" s="17" t="s">
+      <c r="A450" s="17"/>
+      <c r="B450" s="12" t="s">
         <v>181</v>
       </c>
       <c r="C450" s="4">
@@ -19438,8 +19438,8 @@
       <c r="K450" s="6"/>
     </row>
     <row r="451" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A451" s="11"/>
-      <c r="B451" s="17" t="s">
+      <c r="A451" s="17"/>
+      <c r="B451" s="12" t="s">
         <v>182</v>
       </c>
       <c r="C451" s="4">
@@ -19469,8 +19469,8 @@
       <c r="K451" s="6"/>
     </row>
     <row r="452" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A452" s="11"/>
-      <c r="B452" s="17" t="s">
+      <c r="A452" s="17"/>
+      <c r="B452" s="12" t="s">
         <v>183</v>
       </c>
       <c r="C452" s="4">
@@ -19500,8 +19500,8 @@
       <c r="K452" s="6"/>
     </row>
     <row r="453" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A453" s="11"/>
-      <c r="B453" s="17" t="s">
+      <c r="A453" s="17"/>
+      <c r="B453" s="12" t="s">
         <v>184</v>
       </c>
       <c r="C453" s="4">
@@ -19531,8 +19531,8 @@
       <c r="K453" s="6"/>
     </row>
     <row r="454" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A454" s="11"/>
-      <c r="B454" s="17" t="s">
+      <c r="A454" s="17"/>
+      <c r="B454" s="12" t="s">
         <v>185</v>
       </c>
       <c r="C454" s="4">
@@ -19562,10 +19562,10 @@
       <c r="K454" s="6"/>
     </row>
     <row r="455" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A455" s="11" t="s">
+      <c r="A455" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B455" s="17" t="s">
+      <c r="B455" s="12" t="s">
         <v>186</v>
       </c>
       <c r="C455" s="4">
@@ -19595,8 +19595,8 @@
       <c r="K455" s="6"/>
     </row>
     <row r="456" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A456" s="11"/>
-      <c r="B456" s="17" t="s">
+      <c r="A456" s="17"/>
+      <c r="B456" s="12" t="s">
         <v>187</v>
       </c>
       <c r="C456" s="4">
@@ -19626,8 +19626,8 @@
       <c r="K456" s="6"/>
     </row>
     <row r="457" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A457" s="11"/>
-      <c r="B457" s="17" t="s">
+      <c r="A457" s="17"/>
+      <c r="B457" s="12" t="s">
         <v>188</v>
       </c>
       <c r="C457" s="4">
@@ -19657,8 +19657,8 @@
       <c r="K457" s="6"/>
     </row>
     <row r="458" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A458" s="11"/>
-      <c r="B458" s="17" t="s">
+      <c r="A458" s="17"/>
+      <c r="B458" s="12" t="s">
         <v>189</v>
       </c>
       <c r="C458" s="4">
@@ -19688,8 +19688,8 @@
       <c r="K458" s="6"/>
     </row>
     <row r="459" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A459" s="11"/>
-      <c r="B459" s="17" t="s">
+      <c r="A459" s="17"/>
+      <c r="B459" s="12" t="s">
         <v>190</v>
       </c>
       <c r="C459" s="4">
@@ -19719,8 +19719,8 @@
       <c r="K459" s="6"/>
     </row>
     <row r="460" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A460" s="11"/>
-      <c r="B460" s="17" t="s">
+      <c r="A460" s="17"/>
+      <c r="B460" s="12" t="s">
         <v>191</v>
       </c>
       <c r="C460" s="4">
@@ -19750,8 +19750,8 @@
       <c r="K460" s="6"/>
     </row>
     <row r="461" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A461" s="11"/>
-      <c r="B461" s="17" t="s">
+      <c r="A461" s="17"/>
+      <c r="B461" s="12" t="s">
         <v>192</v>
       </c>
       <c r="C461" s="4">
@@ -19781,8 +19781,8 @@
       <c r="K461" s="6"/>
     </row>
     <row r="462" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A462" s="11"/>
-      <c r="B462" s="17" t="s">
+      <c r="A462" s="17"/>
+      <c r="B462" s="12" t="s">
         <v>193</v>
       </c>
       <c r="C462" s="4">
@@ -19812,8 +19812,8 @@
       <c r="K462" s="6"/>
     </row>
     <row r="463" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A463" s="11"/>
-      <c r="B463" s="17" t="s">
+      <c r="A463" s="17"/>
+      <c r="B463" s="12" t="s">
         <v>194</v>
       </c>
       <c r="C463" s="4">
@@ -19843,8 +19843,8 @@
       <c r="K463" s="6"/>
     </row>
     <row r="464" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A464" s="11"/>
-      <c r="B464" s="17" t="s">
+      <c r="A464" s="17"/>
+      <c r="B464" s="12" t="s">
         <v>195</v>
       </c>
       <c r="C464" s="4">
@@ -19874,8 +19874,8 @@
       <c r="K464" s="6"/>
     </row>
     <row r="465" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A465" s="11"/>
-      <c r="B465" s="17" t="s">
+      <c r="A465" s="17"/>
+      <c r="B465" s="12" t="s">
         <v>196</v>
       </c>
       <c r="C465" s="4">
@@ -19905,8 +19905,8 @@
       <c r="K465" s="6"/>
     </row>
     <row r="466" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A466" s="11"/>
-      <c r="B466" s="17" t="s">
+      <c r="A466" s="17"/>
+      <c r="B466" s="12" t="s">
         <v>197</v>
       </c>
       <c r="C466" s="4">
@@ -19936,8 +19936,8 @@
       <c r="K466" s="6"/>
     </row>
     <row r="467" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A467" s="11"/>
-      <c r="B467" s="17" t="s">
+      <c r="A467" s="17"/>
+      <c r="B467" s="12" t="s">
         <v>198</v>
       </c>
       <c r="C467" s="4">
@@ -19967,8 +19967,8 @@
       <c r="K467" s="6"/>
     </row>
     <row r="468" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A468" s="11"/>
-      <c r="B468" s="17" t="s">
+      <c r="A468" s="17"/>
+      <c r="B468" s="12" t="s">
         <v>199</v>
       </c>
       <c r="C468" s="4">
@@ -19998,8 +19998,8 @@
       <c r="K468" s="6"/>
     </row>
     <row r="469" spans="1:11" ht="15" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A469" s="11"/>
-      <c r="B469" s="17" t="s">
+      <c r="A469" s="17"/>
+      <c r="B469" s="12" t="s">
         <v>200</v>
       </c>
       <c r="C469" s="4">
@@ -20029,8 +20029,8 @@
       <c r="K469" s="6"/>
     </row>
     <row r="470" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A470" s="11"/>
-      <c r="B470" s="17" t="s">
+      <c r="A470" s="17"/>
+      <c r="B470" s="12" t="s">
         <v>201</v>
       </c>
       <c r="C470" s="4">
